--- a/samples/예시데이터_시험일지정리.xlsx
+++ b/samples/예시데이터_시험일지정리.xlsx
@@ -415,7 +415,7 @@
         <v>누적 가동시간(h)</v>
       </c>
       <c r="E1">
-        <v>566</v>
+        <v>572</v>
       </c>
     </row>
     <row r="2">
@@ -429,13 +429,13 @@
         <v>누적 Ratio</v>
       </c>
       <c r="D2" t="str">
-        <v>94.3%</v>
+        <v>95.3%</v>
       </c>
       <c r="E2" t="str">
         <v>누적 아워미터(h)</v>
       </c>
       <c r="F2">
-        <v>1806</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="3">
@@ -449,13 +449,13 @@
         <v>남은 시간(h)</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E3" t="str">
         <v>경유 합계(L)</v>
       </c>
       <c r="F3">
-        <v>1297.8</v>
+        <v>1325.7</v>
       </c>
       <c r="G3" t="str">
         <v>요소수 합계(L)</v>
@@ -481,13 +481,13 @@
         <v>기본 사이클 합계(회)</v>
       </c>
       <c r="F4">
-        <v>2612</v>
+        <v>2642</v>
       </c>
       <c r="G4" t="str">
         <v>요철 사이클 합계(회)</v>
       </c>
       <c r="H4">
-        <v>509</v>
+        <v>514</v>
       </c>
     </row>
     <row r="6">
@@ -657,22 +657,22 @@
         <v>야</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="D9">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="E9">
-        <v>20.5</v>
+        <v>18.5</v>
       </c>
       <c r="F9">
-        <v>1260.5</v>
+        <v>1258.5</v>
       </c>
       <c r="G9">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>0.5</v>
@@ -684,7 +684,7 @@
         <v/>
       </c>
       <c r="L9">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="M9" t="str">
         <v/>
@@ -710,22 +710,22 @@
         <v>주</v>
       </c>
       <c r="C10">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="D10">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="E10">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F10">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="G10">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I10">
         <v>0.5</v>
@@ -737,7 +737,7 @@
         <v/>
       </c>
       <c r="L10">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="M10" t="str">
         <v/>
@@ -763,19 +763,19 @@
         <v>주</v>
       </c>
       <c r="C11">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="D11">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="E11">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>1272.5</v>
+        <v>1272</v>
       </c>
       <c r="G11">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H11">
         <v>5</v>
@@ -790,16 +790,16 @@
         <v/>
       </c>
       <c r="L11">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>45.5</v>
+        <v>48.3</v>
       </c>
       <c r="N11" t="str">
         <v/>
       </c>
       <c r="O11" t="str">
-        <v>비</v>
+        <v>맑음</v>
       </c>
       <c r="P11" t="str">
         <v>운전자A</v>
@@ -816,22 +816,22 @@
         <v>주</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="D12">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="E12">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F12">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="G12">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I12">
         <v>0.5</v>
@@ -843,7 +843,7 @@
         <v/>
       </c>
       <c r="L12">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="M12" t="str">
         <v/>
@@ -852,7 +852,7 @@
         <v/>
       </c>
       <c r="O12" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P12" t="str">
         <v>운전자B</v>
@@ -875,10 +875,10 @@
         <v>5</v>
       </c>
       <c r="E13">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F13">
-        <v>1285</v>
+        <v>1282</v>
       </c>
       <c r="G13">
         <v>23</v>
@@ -905,7 +905,7 @@
         <v/>
       </c>
       <c r="O13" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P13" t="str">
         <v>운전자D</v>
@@ -928,10 +928,10 @@
         <v>7.5</v>
       </c>
       <c r="E14">
-        <v>52.5</v>
+        <v>49.5</v>
       </c>
       <c r="F14">
-        <v>1292.5</v>
+        <v>1289.5</v>
       </c>
       <c r="G14">
         <v>35</v>
@@ -975,22 +975,22 @@
         <v>주</v>
       </c>
       <c r="C15">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="D15">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="E15">
-        <v>60.5</v>
+        <v>56</v>
       </c>
       <c r="F15">
-        <v>1300.5</v>
+        <v>1296</v>
       </c>
       <c r="G15">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I15">
         <v>0.5</v>
@@ -1002,16 +1002,16 @@
         <v/>
       </c>
       <c r="L15">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="M15">
-        <v>61.6</v>
+        <v>53.7</v>
       </c>
       <c r="N15" t="str">
         <v/>
       </c>
       <c r="O15" t="str">
-        <v>흐림</v>
+        <v>맑음</v>
       </c>
       <c r="P15" t="str">
         <v>운전자D</v>
@@ -1028,22 +1028,22 @@
         <v>야</v>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E16">
-        <v>66.5</v>
+        <v>64</v>
       </c>
       <c r="F16">
-        <v>1306.5</v>
+        <v>1304</v>
       </c>
       <c r="G16">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="H16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I16">
         <v>0.5</v>
@@ -1055,7 +1055,7 @@
         <v/>
       </c>
       <c r="L16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M16" t="str">
         <v/>
@@ -1064,7 +1064,7 @@
         <v/>
       </c>
       <c r="O16" t="str">
-        <v>흐림</v>
+        <v>맑음</v>
       </c>
       <c r="P16" t="str">
         <v>운전자B</v>
@@ -1081,22 +1081,22 @@
         <v>주</v>
       </c>
       <c r="C17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17">
-        <v>74.5</v>
+        <v>71</v>
       </c>
       <c r="F17">
-        <v>1314.5</v>
+        <v>1311</v>
       </c>
       <c r="G17">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I17">
         <v>0.5</v>
@@ -1108,7 +1108,7 @@
         <v/>
       </c>
       <c r="L17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M17" t="str">
         <v/>
@@ -1117,7 +1117,7 @@
         <v/>
       </c>
       <c r="O17" t="str">
-        <v>비</v>
+        <v>맑음</v>
       </c>
       <c r="P17" t="str">
         <v>운전자A</v>
@@ -1140,10 +1140,10 @@
         <v>7</v>
       </c>
       <c r="E18">
-        <v>81.5</v>
+        <v>78</v>
       </c>
       <c r="F18">
-        <v>1321.5</v>
+        <v>1318</v>
       </c>
       <c r="G18">
         <v>32</v>
@@ -1164,7 +1164,7 @@
         <v>7</v>
       </c>
       <c r="M18">
-        <v>60.2</v>
+        <v>61.6</v>
       </c>
       <c r="N18" t="str">
         <v/>
@@ -1187,19 +1187,19 @@
         <v>주</v>
       </c>
       <c r="C19">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="D19">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="E19">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F19">
-        <v>1329</v>
+        <v>1326</v>
       </c>
       <c r="G19">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H19">
         <v>7</v>
@@ -1214,7 +1214,7 @@
         <v/>
       </c>
       <c r="L19">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="M19" t="str">
         <v/>
@@ -1240,22 +1240,22 @@
         <v>야</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E20">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F20">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="G20">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="H20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I20">
         <v>0.5</v>
@@ -1267,7 +1267,7 @@
         <v/>
       </c>
       <c r="L20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M20" t="str">
         <v/>
@@ -1293,22 +1293,22 @@
         <v>주</v>
       </c>
       <c r="C21">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="D21">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="E21">
-        <v>100.5</v>
+        <v>101.5</v>
       </c>
       <c r="F21">
-        <v>1340.5</v>
+        <v>1341.5</v>
       </c>
       <c r="G21">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I21">
         <v>0.5</v>
@@ -1320,7 +1320,7 @@
         <v/>
       </c>
       <c r="L21">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="M21" t="str">
         <v/>
@@ -1329,7 +1329,7 @@
         <v/>
       </c>
       <c r="O21" t="str">
-        <v>비</v>
+        <v>맑음</v>
       </c>
       <c r="P21" t="str">
         <v>운전자D</v>
@@ -1346,22 +1346,22 @@
         <v>주</v>
       </c>
       <c r="C22">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="D22">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="E22">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F22">
-        <v>1346</v>
+        <v>1349</v>
       </c>
       <c r="G22">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I22">
         <v>0.5</v>
@@ -1373,10 +1373,10 @@
         <v/>
       </c>
       <c r="L22">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="M22">
-        <v>48.8</v>
+        <v>56.7</v>
       </c>
       <c r="N22">
         <v>20</v>
@@ -1388,7 +1388,7 @@
         <v>운전자A</v>
       </c>
       <c r="Q22" t="str">
-        <v/>
+        <v>좌측 마스트 체인에서 소음 발생(예시)</v>
       </c>
     </row>
     <row r="23">
@@ -1399,19 +1399,19 @@
         <v>야</v>
       </c>
       <c r="C23">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="D23">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="E23">
-        <v>111.5</v>
+        <v>114</v>
       </c>
       <c r="F23">
-        <v>1351.5</v>
+        <v>1354</v>
       </c>
       <c r="G23">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H23">
         <v>5</v>
@@ -1426,7 +1426,7 @@
         <v/>
       </c>
       <c r="L23">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="M23" t="str">
         <v/>
@@ -1458,10 +1458,10 @@
         <v>7</v>
       </c>
       <c r="E24">
-        <v>118.5</v>
+        <v>121</v>
       </c>
       <c r="F24">
-        <v>1358.5</v>
+        <v>1361</v>
       </c>
       <c r="G24">
         <v>32</v>
@@ -1488,13 +1488,13 @@
         <v/>
       </c>
       <c r="O24" t="str">
-        <v>맑음</v>
+        <v>비</v>
       </c>
       <c r="P24" t="str">
         <v>운전자B</v>
       </c>
       <c r="Q24" t="str">
-        <v>좌측 마스트 체인에서 소음 발생(예시)</v>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -1511,10 +1511,10 @@
         <v>5.5</v>
       </c>
       <c r="E25">
-        <v>124</v>
+        <v>126.5</v>
       </c>
       <c r="F25">
-        <v>1364</v>
+        <v>1366.5</v>
       </c>
       <c r="G25">
         <v>25</v>
@@ -1535,7 +1535,7 @@
         <v>5.5</v>
       </c>
       <c r="M25">
-        <v>49</v>
+        <v>46.3</v>
       </c>
       <c r="N25" t="str">
         <v/>
@@ -1558,22 +1558,22 @@
         <v>주</v>
       </c>
       <c r="C26">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="D26">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="E26">
-        <v>130.5</v>
+        <v>134</v>
       </c>
       <c r="F26">
-        <v>1370.5</v>
+        <v>1374</v>
       </c>
       <c r="G26">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I26">
         <v>0.5</v>
@@ -1585,7 +1585,7 @@
         <v/>
       </c>
       <c r="L26">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="M26" t="str">
         <v/>
@@ -1611,22 +1611,22 @@
         <v>야</v>
       </c>
       <c r="C27">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="D27">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="E27">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F27">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="G27">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I27">
         <v>0.5</v>
@@ -1638,7 +1638,7 @@
         <v/>
       </c>
       <c r="L27">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="M27" t="str">
         <v/>
@@ -1670,10 +1670,10 @@
         <v>6</v>
       </c>
       <c r="E28">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F28">
-        <v>1383</v>
+        <v>1386</v>
       </c>
       <c r="G28">
         <v>28</v>
@@ -1700,7 +1700,7 @@
         <v/>
       </c>
       <c r="O28" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P28" t="str">
         <v>운전자A</v>
@@ -1717,22 +1717,22 @@
         <v>주</v>
       </c>
       <c r="C29">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="E29">
-        <v>149</v>
+        <v>153.5</v>
       </c>
       <c r="F29">
-        <v>1389</v>
+        <v>1393.5</v>
       </c>
       <c r="G29">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I29">
         <v>0.5</v>
@@ -1744,16 +1744,16 @@
         <v/>
       </c>
       <c r="L29">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="M29">
-        <v>52.3</v>
+        <v>62.5</v>
       </c>
       <c r="N29" t="str">
         <v/>
       </c>
       <c r="O29" t="str">
-        <v>맑음</v>
+        <v>비</v>
       </c>
       <c r="P29" t="str">
         <v>운전자B</v>
@@ -1776,10 +1776,10 @@
         <v>6</v>
       </c>
       <c r="E30">
-        <v>155</v>
+        <v>159.5</v>
       </c>
       <c r="F30">
-        <v>1395</v>
+        <v>1399.5</v>
       </c>
       <c r="G30">
         <v>28</v>
@@ -1806,7 +1806,7 @@
         <v/>
       </c>
       <c r="O30" t="str">
-        <v>맑음</v>
+        <v>비</v>
       </c>
       <c r="P30" t="str">
         <v>운전자D</v>
@@ -1823,22 +1823,22 @@
         <v>주</v>
       </c>
       <c r="C31">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="D31">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="E31">
-        <v>162.5</v>
+        <v>165</v>
       </c>
       <c r="F31">
-        <v>1402.5</v>
+        <v>1405</v>
       </c>
       <c r="G31">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I31">
         <v>0.5</v>
@@ -1850,7 +1850,7 @@
         <v/>
       </c>
       <c r="L31">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="M31" t="str">
         <v/>
@@ -1859,7 +1859,7 @@
         <v/>
       </c>
       <c r="O31" t="str">
-        <v>비</v>
+        <v>맑음</v>
       </c>
       <c r="P31" t="str">
         <v>운전자C</v>
@@ -1882,10 +1882,10 @@
         <v>7.5</v>
       </c>
       <c r="E32">
-        <v>170</v>
+        <v>172.5</v>
       </c>
       <c r="F32">
-        <v>1410</v>
+        <v>1412.5</v>
       </c>
       <c r="G32">
         <v>35</v>
@@ -1906,13 +1906,13 @@
         <v>7.5</v>
       </c>
       <c r="M32">
-        <v>60.9</v>
+        <v>60.4</v>
       </c>
       <c r="N32" t="str">
         <v/>
       </c>
       <c r="O32" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P32" t="str">
         <v>운전자D</v>
@@ -1935,10 +1935,10 @@
         <v>5.5</v>
       </c>
       <c r="E33">
-        <v>175.5</v>
+        <v>178</v>
       </c>
       <c r="F33">
-        <v>1415.5</v>
+        <v>1418</v>
       </c>
       <c r="G33">
         <v>25</v>
@@ -1988,10 +1988,10 @@
         <v>7.5</v>
       </c>
       <c r="E34">
-        <v>183</v>
+        <v>185.5</v>
       </c>
       <c r="F34">
-        <v>1423</v>
+        <v>1425.5</v>
       </c>
       <c r="G34">
         <v>35</v>
@@ -2035,22 +2035,22 @@
         <v>주</v>
       </c>
       <c r="C35">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="D35">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="E35">
-        <v>189.5</v>
+        <v>193</v>
       </c>
       <c r="F35">
-        <v>1429.5</v>
+        <v>1433</v>
       </c>
       <c r="G35">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I35">
         <v>0.5</v>
@@ -2062,7 +2062,7 @@
         <v/>
       </c>
       <c r="L35">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="M35" t="str">
         <v/>
@@ -2094,10 +2094,10 @@
         <v>5.5</v>
       </c>
       <c r="E36">
-        <v>195</v>
+        <v>198.5</v>
       </c>
       <c r="F36">
-        <v>1435</v>
+        <v>1438.5</v>
       </c>
       <c r="G36">
         <v>25</v>
@@ -2118,13 +2118,13 @@
         <v>5.5</v>
       </c>
       <c r="M36">
-        <v>49.3</v>
+        <v>44.7</v>
       </c>
       <c r="N36" t="str">
         <v/>
       </c>
       <c r="O36" t="str">
-        <v>맑음</v>
+        <v>비</v>
       </c>
       <c r="P36" t="str">
         <v>운전자C</v>
@@ -2141,22 +2141,22 @@
         <v>야</v>
       </c>
       <c r="C37">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D37">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="E37">
-        <v>200.5</v>
+        <v>205</v>
       </c>
       <c r="F37">
-        <v>1440.5</v>
+        <v>1445</v>
       </c>
       <c r="G37">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I37">
         <v>0.5</v>
@@ -2168,7 +2168,7 @@
         <v/>
       </c>
       <c r="L37">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="M37" t="str">
         <v/>
@@ -2177,7 +2177,7 @@
         <v/>
       </c>
       <c r="O37" t="str">
-        <v>맑음</v>
+        <v>비</v>
       </c>
       <c r="P37" t="str">
         <v>운전자A</v>
@@ -2194,19 +2194,19 @@
         <v>주</v>
       </c>
       <c r="C38">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="D38">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="E38">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F38">
-        <v>1448</v>
+        <v>1453</v>
       </c>
       <c r="G38">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H38">
         <v>7</v>
@@ -2221,7 +2221,7 @@
         <v/>
       </c>
       <c r="L38">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="M38" t="str">
         <v/>
@@ -2230,7 +2230,7 @@
         <v/>
       </c>
       <c r="O38" t="str">
-        <v>흐림</v>
+        <v>비</v>
       </c>
       <c r="P38" t="str">
         <v>운전자D</v>
@@ -2253,10 +2253,10 @@
         <v>6</v>
       </c>
       <c r="E39">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="F39">
-        <v>1454</v>
+        <v>1459</v>
       </c>
       <c r="G39">
         <v>28</v>
@@ -2277,13 +2277,13 @@
         <v>6</v>
       </c>
       <c r="M39">
-        <v>50.2</v>
+        <v>46.5</v>
       </c>
       <c r="N39" t="str">
         <v/>
       </c>
       <c r="O39" t="str">
-        <v>맑음</v>
+        <v>비</v>
       </c>
       <c r="P39" t="str">
         <v>운전자A</v>
@@ -2300,19 +2300,19 @@
         <v>주</v>
       </c>
       <c r="C40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E40">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="F40">
-        <v>1459</v>
+        <v>1465</v>
       </c>
       <c r="G40">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H40">
         <v>5</v>
@@ -2327,7 +2327,7 @@
         <v/>
       </c>
       <c r="L40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M40" t="str">
         <v/>
@@ -2359,10 +2359,10 @@
         <v>8</v>
       </c>
       <c r="E41">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="F41">
-        <v>1467</v>
+        <v>1473</v>
       </c>
       <c r="G41">
         <v>37</v>
@@ -2406,22 +2406,22 @@
         <v>주</v>
       </c>
       <c r="C42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E42">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="F42">
-        <v>1473</v>
+        <v>1480</v>
       </c>
       <c r="G42">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I42">
         <v>0.5</v>
@@ -2433,7 +2433,7 @@
         <v/>
       </c>
       <c r="L42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M42" t="str">
         <v/>
@@ -2442,13 +2442,13 @@
         <v/>
       </c>
       <c r="O42" t="str">
-        <v>비</v>
+        <v>맑음</v>
       </c>
       <c r="P42" t="str">
         <v>운전자C</v>
       </c>
       <c r="Q42" t="str">
-        <v>좌측 마스트 체인에서 소음 발생(예시)</v>
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -2459,22 +2459,22 @@
         <v>주</v>
       </c>
       <c r="C43">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="D43">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="E43">
-        <v>238</v>
+        <v>247.5</v>
       </c>
       <c r="F43">
-        <v>1478</v>
+        <v>1487.5</v>
       </c>
       <c r="G43">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I43">
         <v>0.5</v>
@@ -2486,10 +2486,10 @@
         <v/>
       </c>
       <c r="L43">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="M43">
-        <v>40.9</v>
+        <v>59.5</v>
       </c>
       <c r="N43">
         <v>20</v>
@@ -2512,22 +2512,22 @@
         <v>야</v>
       </c>
       <c r="C44">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D44">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E44">
-        <v>246</v>
+        <v>252.5</v>
       </c>
       <c r="F44">
-        <v>1486</v>
+        <v>1492.5</v>
       </c>
       <c r="G44">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="H44">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I44">
         <v>0.5</v>
@@ -2539,7 +2539,7 @@
         <v/>
       </c>
       <c r="L44">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M44" t="str">
         <v/>
@@ -2565,22 +2565,22 @@
         <v>주</v>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="D45">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="E45">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F45">
-        <v>1493</v>
+        <v>1498</v>
       </c>
       <c r="G45">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I45">
         <v>0.5</v>
@@ -2592,7 +2592,7 @@
         <v/>
       </c>
       <c r="L45">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="M45" t="str">
         <v/>
@@ -2601,7 +2601,7 @@
         <v/>
       </c>
       <c r="O45" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P45" t="str">
         <v>운전자A</v>
@@ -2618,19 +2618,19 @@
         <v>주</v>
       </c>
       <c r="C46">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="D46">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="E46">
-        <v>260.5</v>
+        <v>266</v>
       </c>
       <c r="F46">
-        <v>1500.5</v>
+        <v>1506</v>
       </c>
       <c r="G46">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H46">
         <v>7</v>
@@ -2645,16 +2645,16 @@
         <v/>
       </c>
       <c r="L46">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="M46">
-        <v>59.5</v>
+        <v>62.1</v>
       </c>
       <c r="N46" t="str">
         <v/>
       </c>
       <c r="O46" t="str">
-        <v>비</v>
+        <v>흐림</v>
       </c>
       <c r="P46" t="str">
         <v>운전자B</v>
@@ -2671,22 +2671,22 @@
         <v>주</v>
       </c>
       <c r="C47">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="D47">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="E47">
-        <v>265.5</v>
+        <v>272.5</v>
       </c>
       <c r="F47">
-        <v>1505.5</v>
+        <v>1512.5</v>
       </c>
       <c r="G47">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I47">
         <v>0.5</v>
@@ -2698,7 +2698,7 @@
         <v/>
       </c>
       <c r="L47">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="M47" t="str">
         <v/>
@@ -2730,10 +2730,10 @@
         <v>7.5</v>
       </c>
       <c r="E48">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="F48">
-        <v>1513</v>
+        <v>1520</v>
       </c>
       <c r="G48">
         <v>35</v>
@@ -2777,22 +2777,22 @@
         <v>주</v>
       </c>
       <c r="C49">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="D49">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="E49">
-        <v>280.5</v>
+        <v>285.5</v>
       </c>
       <c r="F49">
-        <v>1520.5</v>
+        <v>1525.5</v>
       </c>
       <c r="G49">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H49">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I49">
         <v>0.5</v>
@@ -2804,7 +2804,7 @@
         <v/>
       </c>
       <c r="L49">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="M49" t="str">
         <v/>
@@ -2813,13 +2813,13 @@
         <v/>
       </c>
       <c r="O49" t="str">
-        <v>비</v>
+        <v>맑음</v>
       </c>
       <c r="P49" t="str">
         <v>운전자D</v>
       </c>
       <c r="Q49" t="str">
-        <v/>
+        <v>좌측 마스트 체인에서 소음 발생(예시)</v>
       </c>
     </row>
     <row r="50">
@@ -2830,22 +2830,22 @@
         <v>주</v>
       </c>
       <c r="C50">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D50">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E50">
-        <v>286.5</v>
+        <v>293.5</v>
       </c>
       <c r="F50">
-        <v>1526.5</v>
+        <v>1533.5</v>
       </c>
       <c r="G50">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="H50">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I50">
         <v>0.5</v>
@@ -2857,22 +2857,22 @@
         <v/>
       </c>
       <c r="L50">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M50">
-        <v>54.5</v>
+        <v>70</v>
       </c>
       <c r="N50" t="str">
         <v/>
       </c>
       <c r="O50" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P50" t="str">
         <v>운전자A</v>
       </c>
       <c r="Q50" t="str">
-        <v>브레이크 페달 유격 커짐(예시)</v>
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -2883,22 +2883,22 @@
         <v>야</v>
       </c>
       <c r="C51">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="D51">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="E51">
-        <v>293</v>
+        <v>299.5</v>
       </c>
       <c r="F51">
-        <v>1533</v>
+        <v>1539.5</v>
       </c>
       <c r="G51">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H51">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I51">
         <v>0.5</v>
@@ -2910,7 +2910,7 @@
         <v/>
       </c>
       <c r="L51">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="M51" t="str">
         <v/>
@@ -2919,13 +2919,13 @@
         <v/>
       </c>
       <c r="O51" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P51" t="str">
         <v>운전자C</v>
       </c>
       <c r="Q51" t="str">
-        <v/>
+        <v>브레이크 페달 유격 커짐(예시)</v>
       </c>
     </row>
     <row r="52">
@@ -2936,19 +2936,19 @@
         <v>주</v>
       </c>
       <c r="C52">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="D52">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="E52">
-        <v>299.5</v>
+        <v>306.5</v>
       </c>
       <c r="F52">
-        <v>1539.5</v>
+        <v>1546.5</v>
       </c>
       <c r="G52">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H52">
         <v>6</v>
@@ -2963,7 +2963,7 @@
         <v/>
       </c>
       <c r="L52">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="M52" t="str">
         <v/>
@@ -2972,7 +2972,7 @@
         <v/>
       </c>
       <c r="O52" t="str">
-        <v>비</v>
+        <v>흐림</v>
       </c>
       <c r="P52" t="str">
         <v>운전자B</v>
@@ -2989,22 +2989,22 @@
         <v>주</v>
       </c>
       <c r="C53">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D53">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E53">
-        <v>304.5</v>
+        <v>313.5</v>
       </c>
       <c r="F53">
-        <v>1544.5</v>
+        <v>1553.5</v>
       </c>
       <c r="G53">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H53">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I53">
         <v>0.5</v>
@@ -3016,10 +3016,10 @@
         <v/>
       </c>
       <c r="L53">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M53">
-        <v>43.9</v>
+        <v>59.4</v>
       </c>
       <c r="N53" t="str">
         <v/>
@@ -3042,22 +3042,22 @@
         <v>주</v>
       </c>
       <c r="C54">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="D54">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="E54">
-        <v>309.5</v>
+        <v>321</v>
       </c>
       <c r="F54">
-        <v>1549.5</v>
+        <v>1561</v>
       </c>
       <c r="G54">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H54">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I54">
         <v>0.5</v>
@@ -3069,7 +3069,7 @@
         <v/>
       </c>
       <c r="L54">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="M54" t="str">
         <v/>
@@ -3078,7 +3078,7 @@
         <v/>
       </c>
       <c r="O54" t="str">
-        <v>흐림</v>
+        <v>맑음</v>
       </c>
       <c r="P54" t="str">
         <v>운전자D</v>
@@ -3095,19 +3095,19 @@
         <v>야</v>
       </c>
       <c r="C55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E55">
-        <v>315.5</v>
+        <v>326</v>
       </c>
       <c r="F55">
-        <v>1555.5</v>
+        <v>1566</v>
       </c>
       <c r="G55">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H55">
         <v>5</v>
@@ -3122,7 +3122,7 @@
         <v/>
       </c>
       <c r="L55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M55" t="str">
         <v/>
@@ -3131,13 +3131,13 @@
         <v/>
       </c>
       <c r="O55" t="str">
-        <v>흐림</v>
+        <v>맑음</v>
       </c>
       <c r="P55" t="str">
         <v>운전자B</v>
       </c>
       <c r="Q55" t="str">
-        <v>브레이크 페달 유격 커짐(예시)</v>
+        <v/>
       </c>
     </row>
     <row r="56">
@@ -3154,10 +3154,10 @@
         <v>7</v>
       </c>
       <c r="E56">
-        <v>322.5</v>
+        <v>333</v>
       </c>
       <c r="F56">
-        <v>1562.5</v>
+        <v>1573</v>
       </c>
       <c r="G56">
         <v>32</v>
@@ -3201,22 +3201,22 @@
         <v>주</v>
       </c>
       <c r="C57">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D57">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E57">
-        <v>329.5</v>
+        <v>338</v>
       </c>
       <c r="F57">
-        <v>1569.5</v>
+        <v>1578</v>
       </c>
       <c r="G57">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H57">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I57">
         <v>0.5</v>
@@ -3228,16 +3228,16 @@
         <v/>
       </c>
       <c r="L57">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M57">
-        <v>59.4</v>
+        <v>40.9</v>
       </c>
       <c r="N57" t="str">
         <v/>
       </c>
       <c r="O57" t="str">
-        <v>맑음</v>
+        <v>비</v>
       </c>
       <c r="P57" t="str">
         <v>운전자B</v>
@@ -3260,10 +3260,10 @@
         <v>7</v>
       </c>
       <c r="E58">
-        <v>336.5</v>
+        <v>345</v>
       </c>
       <c r="F58">
-        <v>1576.5</v>
+        <v>1585</v>
       </c>
       <c r="G58">
         <v>32</v>
@@ -3290,7 +3290,7 @@
         <v/>
       </c>
       <c r="O58" t="str">
-        <v>맑음</v>
+        <v>비</v>
       </c>
       <c r="P58" t="str">
         <v>운전자D</v>
@@ -3307,22 +3307,22 @@
         <v>주</v>
       </c>
       <c r="C59">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="D59">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="E59">
-        <v>343.5</v>
+        <v>350.5</v>
       </c>
       <c r="F59">
-        <v>1583.5</v>
+        <v>1590.5</v>
       </c>
       <c r="G59">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H59">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I59">
         <v>0.5</v>
@@ -3334,7 +3334,7 @@
         <v/>
       </c>
       <c r="L59">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="M59" t="str">
         <v/>
@@ -3349,7 +3349,7 @@
         <v>운전자C</v>
       </c>
       <c r="Q59" t="str">
-        <v>충전 커넥터 체결 불량(예시)</v>
+        <v/>
       </c>
     </row>
     <row r="60">
@@ -3360,22 +3360,22 @@
         <v>주</v>
       </c>
       <c r="C60">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D60">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E60">
-        <v>350.5</v>
+        <v>356.5</v>
       </c>
       <c r="F60">
-        <v>1590.5</v>
+        <v>1596.5</v>
       </c>
       <c r="G60">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H60">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I60">
         <v>0.5</v>
@@ -3387,22 +3387,22 @@
         <v/>
       </c>
       <c r="L60">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M60">
-        <v>55</v>
+        <v>45.8</v>
       </c>
       <c r="N60" t="str">
         <v/>
       </c>
       <c r="O60" t="str">
-        <v>흐림</v>
+        <v>맑음</v>
       </c>
       <c r="P60" t="str">
         <v>운전자D</v>
       </c>
       <c r="Q60" t="str">
-        <v/>
+        <v>좌측 마스트 체인에서 소음 발생(예시)</v>
       </c>
     </row>
     <row r="61">
@@ -3413,22 +3413,22 @@
         <v>주</v>
       </c>
       <c r="C61">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="D61">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="E61">
-        <v>356.5</v>
+        <v>363</v>
       </c>
       <c r="F61">
-        <v>1596.5</v>
+        <v>1603</v>
       </c>
       <c r="G61">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H61">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I61">
         <v>0.5</v>
@@ -3440,7 +3440,7 @@
         <v/>
       </c>
       <c r="L61">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="M61" t="str">
         <v/>
@@ -3466,19 +3466,19 @@
         <v>야</v>
       </c>
       <c r="C62">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="D62">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="E62">
-        <v>364.5</v>
+        <v>370.5</v>
       </c>
       <c r="F62">
-        <v>1604.5</v>
+        <v>1610.5</v>
       </c>
       <c r="G62">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H62">
         <v>7</v>
@@ -3493,7 +3493,7 @@
         <v/>
       </c>
       <c r="L62">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="M62" t="str">
         <v/>
@@ -3508,7 +3508,7 @@
         <v>운전자C</v>
       </c>
       <c r="Q62" t="str">
-        <v/>
+        <v>작동유 온도 경고등 점등 후 소등(예시)</v>
       </c>
     </row>
     <row r="63">
@@ -3519,22 +3519,22 @@
         <v>주</v>
       </c>
       <c r="C63">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="D63">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="E63">
-        <v>371.5</v>
+        <v>378</v>
       </c>
       <c r="F63">
-        <v>1611.5</v>
+        <v>1618</v>
       </c>
       <c r="G63">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H63">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I63">
         <v>0.5</v>
@@ -3546,7 +3546,7 @@
         <v/>
       </c>
       <c r="L63">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="M63" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v/>
       </c>
       <c r="O63" t="str">
-        <v>비</v>
+        <v>맑음</v>
       </c>
       <c r="P63" t="str">
         <v>운전자B</v>
@@ -3572,22 +3572,22 @@
         <v>주</v>
       </c>
       <c r="C64">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="D64">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="E64">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="F64">
-        <v>1618</v>
+        <v>1626</v>
       </c>
       <c r="G64">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H64">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I64">
         <v>0.5</v>
@@ -3599,22 +3599,22 @@
         <v/>
       </c>
       <c r="L64">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="M64">
-        <v>53.6</v>
+        <v>64.8</v>
       </c>
       <c r="N64">
         <v>20</v>
       </c>
       <c r="O64" t="str">
-        <v>맑음</v>
+        <v>비</v>
       </c>
       <c r="P64" t="str">
         <v>운전자C</v>
       </c>
       <c r="Q64" t="str">
-        <v>포크 하강 속도 느려짐(예시)</v>
+        <v/>
       </c>
     </row>
     <row r="65">
@@ -3631,10 +3631,10 @@
         <v>5</v>
       </c>
       <c r="E65">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F65">
-        <v>1623</v>
+        <v>1631</v>
       </c>
       <c r="G65">
         <v>23</v>
@@ -3661,13 +3661,13 @@
         <v/>
       </c>
       <c r="O65" t="str">
-        <v>맑음</v>
+        <v>비</v>
       </c>
       <c r="P65" t="str">
         <v>운전자A</v>
       </c>
       <c r="Q65" t="str">
-        <v>운전석 계기판 화면 깜빡임(예시)</v>
+        <v>충전 커넥터 체결 불량(예시)</v>
       </c>
     </row>
     <row r="66">
@@ -3678,22 +3678,22 @@
         <v>주</v>
       </c>
       <c r="C66">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D66">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E66">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="F66">
-        <v>1631</v>
+        <v>1638</v>
       </c>
       <c r="G66">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H66">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I66">
         <v>0.5</v>
@@ -3705,7 +3705,7 @@
         <v/>
       </c>
       <c r="L66">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M66" t="str">
         <v/>
@@ -3731,19 +3731,19 @@
         <v>주</v>
       </c>
       <c r="C67">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="D67">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="E67">
-        <v>396.5</v>
+        <v>404</v>
       </c>
       <c r="F67">
-        <v>1636.5</v>
+        <v>1644</v>
       </c>
       <c r="G67">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H67">
         <v>5</v>
@@ -3758,10 +3758,10 @@
         <v/>
       </c>
       <c r="L67">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="M67">
-        <v>44.9</v>
+        <v>52.1</v>
       </c>
       <c r="N67" t="str">
         <v/>
@@ -3784,22 +3784,22 @@
         <v>주</v>
       </c>
       <c r="C68">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="D68">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="E68">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="F68">
-        <v>1644</v>
+        <v>1650</v>
       </c>
       <c r="G68">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H68">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I68">
         <v>0.5</v>
@@ -3820,7 +3820,7 @@
         <v/>
       </c>
       <c r="O68" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P68" t="str">
         <v>운전자B</v>
@@ -3837,22 +3837,22 @@
         <v>야</v>
       </c>
       <c r="C69">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="D69">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="E69">
-        <v>410</v>
+        <v>416.5</v>
       </c>
       <c r="F69">
-        <v>1650</v>
+        <v>1656.5</v>
       </c>
       <c r="G69">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I69">
         <v>0.5</v>
@@ -3873,7 +3873,7 @@
         <v/>
       </c>
       <c r="O69" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P69" t="str">
         <v>운전자D</v>
@@ -3890,22 +3890,22 @@
         <v>주</v>
       </c>
       <c r="C70">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D70">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E70">
-        <v>415</v>
+        <v>423.5</v>
       </c>
       <c r="F70">
-        <v>1655</v>
+        <v>1663.5</v>
       </c>
       <c r="G70">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I70">
         <v>0.5</v>
@@ -3932,7 +3932,7 @@
         <v>운전자C</v>
       </c>
       <c r="Q70" t="str">
-        <v>충전 커넥터 체결 불량(예시)</v>
+        <v/>
       </c>
     </row>
     <row r="71">
@@ -3943,22 +3943,22 @@
         <v>주</v>
       </c>
       <c r="C71">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D71">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E71">
-        <v>422</v>
+        <v>428.5</v>
       </c>
       <c r="F71">
-        <v>1662</v>
+        <v>1668.5</v>
       </c>
       <c r="G71">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I71">
         <v>0.5</v>
@@ -3973,13 +3973,13 @@
         <v/>
       </c>
       <c r="M71">
-        <v>57.2</v>
+        <v>38.3</v>
       </c>
       <c r="N71" t="str">
         <v/>
       </c>
       <c r="O71" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P71" t="str">
         <v>운전자D</v>
@@ -3996,19 +3996,19 @@
         <v>야</v>
       </c>
       <c r="C72">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="D72">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="E72">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="F72">
-        <v>1668</v>
+        <v>1674</v>
       </c>
       <c r="G72">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H72">
         <v>5</v>
@@ -4032,7 +4032,7 @@
         <v/>
       </c>
       <c r="O72" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P72" t="str">
         <v>운전자B</v>
@@ -4049,22 +4049,22 @@
         <v>주</v>
       </c>
       <c r="C73">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="D73">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="E73">
-        <v>434.5</v>
+        <v>439</v>
       </c>
       <c r="F73">
-        <v>1674.5</v>
+        <v>1679</v>
       </c>
       <c r="G73">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H73">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I73">
         <v>0.5</v>
@@ -4085,7 +4085,7 @@
         <v/>
       </c>
       <c r="O73" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P73" t="str">
         <v>운전자A</v>
@@ -4108,10 +4108,10 @@
         <v>6</v>
       </c>
       <c r="E74">
-        <v>440.5</v>
+        <v>445</v>
       </c>
       <c r="F74">
-        <v>1680.5</v>
+        <v>1685</v>
       </c>
       <c r="G74">
         <v>28</v>
@@ -4132,7 +4132,7 @@
         <v/>
       </c>
       <c r="M74">
-        <v>50.6</v>
+        <v>53.2</v>
       </c>
       <c r="N74" t="str">
         <v/>
@@ -4155,22 +4155,22 @@
         <v>주</v>
       </c>
       <c r="C75">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="D75">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="E75">
-        <v>447.5</v>
+        <v>450.5</v>
       </c>
       <c r="F75">
-        <v>1687.5</v>
+        <v>1690.5</v>
       </c>
       <c r="G75">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I75">
         <v>0.5</v>
@@ -4208,22 +4208,22 @@
         <v>야</v>
       </c>
       <c r="C76">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D76">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E76">
-        <v>454.5</v>
+        <v>456.5</v>
       </c>
       <c r="F76">
-        <v>1694.5</v>
+        <v>1696.5</v>
       </c>
       <c r="G76">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H76">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I76">
         <v>0.5</v>
@@ -4250,7 +4250,7 @@
         <v>운전자A</v>
       </c>
       <c r="Q76" t="str">
-        <v>좌측 마스트 체인에서 소음 발생(예시)</v>
+        <v/>
       </c>
     </row>
     <row r="77">
@@ -4261,22 +4261,22 @@
         <v>주</v>
       </c>
       <c r="C77">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="D77">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="E77">
-        <v>461</v>
+        <v>461.5</v>
       </c>
       <c r="F77">
-        <v>1701</v>
+        <v>1701.5</v>
       </c>
       <c r="G77">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H77">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I77">
         <v>0.5</v>
@@ -4314,10 +4314,10 @@
         <v>주</v>
       </c>
       <c r="C78">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="D78">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="E78">
         <v>468.5</v>
@@ -4326,10 +4326,10 @@
         <v>1708.5</v>
       </c>
       <c r="G78">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H78">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I78">
         <v>0.5</v>
@@ -4344,7 +4344,7 @@
         <v/>
       </c>
       <c r="M78">
-        <v>58</v>
+        <v>61.8</v>
       </c>
       <c r="N78" t="str">
         <v/>
@@ -4367,19 +4367,19 @@
         <v>야</v>
       </c>
       <c r="C79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E79">
-        <v>473.5</v>
+        <v>474.5</v>
       </c>
       <c r="F79">
-        <v>1713.5</v>
+        <v>1714.5</v>
       </c>
       <c r="G79">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H79">
         <v>5</v>
@@ -4420,22 +4420,22 @@
         <v>주</v>
       </c>
       <c r="C80">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="D80">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="E80">
-        <v>480</v>
+        <v>479.5</v>
       </c>
       <c r="F80">
-        <v>1720</v>
+        <v>1719.5</v>
       </c>
       <c r="G80">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H80">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I80">
         <v>0.5</v>
@@ -4456,7 +4456,7 @@
         <v/>
       </c>
       <c r="O80" t="str">
-        <v>흐림</v>
+        <v>맑음</v>
       </c>
       <c r="P80" t="str">
         <v>운전자B</v>
@@ -4473,19 +4473,19 @@
         <v>주</v>
       </c>
       <c r="C81">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="D81">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="E81">
-        <v>485.5</v>
+        <v>484.5</v>
       </c>
       <c r="F81">
-        <v>1725.5</v>
+        <v>1724.5</v>
       </c>
       <c r="G81">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H81">
         <v>5</v>
@@ -4503,7 +4503,7 @@
         <v/>
       </c>
       <c r="M81">
-        <v>46.6</v>
+        <v>38</v>
       </c>
       <c r="N81" t="str">
         <v/>
@@ -4526,22 +4526,22 @@
         <v>주</v>
       </c>
       <c r="C82">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="D82">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="E82">
-        <v>492</v>
+        <v>492.5</v>
       </c>
       <c r="F82">
-        <v>1732</v>
+        <v>1732.5</v>
       </c>
       <c r="G82">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H82">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I82">
         <v>0.5</v>
@@ -4568,7 +4568,7 @@
         <v>운전자D</v>
       </c>
       <c r="Q82" t="str">
-        <v>작동유 온도 경고등 점등 후 소등(예시)</v>
+        <v/>
       </c>
     </row>
     <row r="83">
@@ -4579,22 +4579,22 @@
         <v>야</v>
       </c>
       <c r="C83">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D83">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E83">
-        <v>498</v>
+        <v>499.5</v>
       </c>
       <c r="F83">
-        <v>1738</v>
+        <v>1739.5</v>
       </c>
       <c r="G83">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H83">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I83">
         <v>0.5</v>
@@ -4632,22 +4632,22 @@
         <v>주</v>
       </c>
       <c r="C84">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="D84">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="E84">
-        <v>503.5</v>
+        <v>507.5</v>
       </c>
       <c r="F84">
-        <v>1743.5</v>
+        <v>1747.5</v>
       </c>
       <c r="G84">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="H84">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I84">
         <v>0.5</v>
@@ -4668,7 +4668,7 @@
         <v/>
       </c>
       <c r="O84" t="str">
-        <v>흐림</v>
+        <v>맑음</v>
       </c>
       <c r="P84" t="str">
         <v>운전자A</v>
@@ -4685,22 +4685,22 @@
         <v>주</v>
       </c>
       <c r="C85">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="D85">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="E85">
-        <v>511</v>
+        <v>513.5</v>
       </c>
       <c r="F85">
-        <v>1751</v>
+        <v>1753.5</v>
       </c>
       <c r="G85">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H85">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I85">
         <v>0.5</v>
@@ -4715,19 +4715,19 @@
         <v/>
       </c>
       <c r="M85">
-        <v>58.4</v>
+        <v>46.9</v>
       </c>
       <c r="N85">
         <v>20</v>
       </c>
       <c r="O85" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P85" t="str">
         <v>운전자B</v>
       </c>
       <c r="Q85" t="str">
-        <v>작동유 온도 경고등 점등 후 소등(예시)</v>
+        <v/>
       </c>
     </row>
     <row r="86">
@@ -4738,22 +4738,22 @@
         <v>야</v>
       </c>
       <c r="C86">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="D86">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="E86">
-        <v>516.5</v>
+        <v>521.5</v>
       </c>
       <c r="F86">
-        <v>1756.5</v>
+        <v>1761.5</v>
       </c>
       <c r="G86">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="H86">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I86">
         <v>0.5</v>
@@ -4774,13 +4774,13 @@
         <v/>
       </c>
       <c r="O86" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P86" t="str">
         <v>운전자D</v>
       </c>
       <c r="Q86" t="str">
-        <v>좌측 마스트 체인에서 소음 발생(예시)</v>
+        <v>브레이크 페달 유격 커짐(예시)</v>
       </c>
     </row>
     <row r="87">
@@ -4791,22 +4791,22 @@
         <v>주</v>
       </c>
       <c r="C87">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D87">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E87">
-        <v>523.5</v>
+        <v>527.5</v>
       </c>
       <c r="F87">
-        <v>1763.5</v>
+        <v>1767.5</v>
       </c>
       <c r="G87">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H87">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I87">
         <v>0.5</v>
@@ -4827,7 +4827,7 @@
         <v/>
       </c>
       <c r="O87" t="str">
-        <v>맑음</v>
+        <v>비</v>
       </c>
       <c r="P87" t="str">
         <v>운전자C</v>
@@ -4850,10 +4850,10 @@
         <v>5.5</v>
       </c>
       <c r="E88">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="F88">
-        <v>1769</v>
+        <v>1773</v>
       </c>
       <c r="G88">
         <v>25</v>
@@ -4874,19 +4874,19 @@
         <v/>
       </c>
       <c r="M88">
-        <v>47</v>
+        <v>43.7</v>
       </c>
       <c r="N88" t="str">
         <v/>
       </c>
       <c r="O88" t="str">
-        <v>비</v>
+        <v>맑음</v>
       </c>
       <c r="P88" t="str">
         <v>운전자D</v>
       </c>
       <c r="Q88" t="str">
-        <v/>
+        <v>브레이크 페달 유격 커짐(예시)</v>
       </c>
     </row>
     <row r="89">
@@ -4897,22 +4897,22 @@
         <v>주</v>
       </c>
       <c r="C89">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D89">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E89">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F89">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="G89">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="H89">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I89">
         <v>0.5</v>
@@ -4933,7 +4933,7 @@
         <v/>
       </c>
       <c r="O89" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P89" t="str">
         <v>운전자A</v>
@@ -4956,10 +4956,10 @@
         <v>7</v>
       </c>
       <c r="E90">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F90">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="G90">
         <v>32</v>
@@ -4986,7 +4986,7 @@
         <v/>
       </c>
       <c r="O90" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P90" t="str">
         <v>운전자C</v>
@@ -5003,22 +5003,22 @@
         <v>주</v>
       </c>
       <c r="C91">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="D91">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="E91">
-        <v>549.5</v>
+        <v>552</v>
       </c>
       <c r="F91">
-        <v>1789.5</v>
+        <v>1792</v>
       </c>
       <c r="G91">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H91">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I91">
         <v>0.5</v>
@@ -5056,22 +5056,22 @@
         <v>주</v>
       </c>
       <c r="C92">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="D92">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="E92">
-        <v>554.5</v>
+        <v>559.5</v>
       </c>
       <c r="F92">
-        <v>1794.5</v>
+        <v>1799.5</v>
       </c>
       <c r="G92">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H92">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I92">
         <v>0.5</v>
@@ -5086,13 +5086,13 @@
         <v/>
       </c>
       <c r="M92">
-        <v>42.8</v>
+        <v>60.8</v>
       </c>
       <c r="N92" t="str">
         <v/>
       </c>
       <c r="O92" t="str">
-        <v>비</v>
+        <v>맑음</v>
       </c>
       <c r="P92" t="str">
         <v>운전자C</v>
@@ -5115,10 +5115,10 @@
         <v>6</v>
       </c>
       <c r="E93">
-        <v>560.5</v>
+        <v>565.5</v>
       </c>
       <c r="F93">
-        <v>1800.5</v>
+        <v>1805.5</v>
       </c>
       <c r="G93">
         <v>28</v>
@@ -5145,7 +5145,7 @@
         <v/>
       </c>
       <c r="O93" t="str">
-        <v>비</v>
+        <v>맑음</v>
       </c>
       <c r="P93" t="str">
         <v>운전자A</v>
@@ -5162,22 +5162,22 @@
         <v>주</v>
       </c>
       <c r="C94">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D94">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="E94">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="F94">
-        <v>1806</v>
+        <v>1812</v>
       </c>
       <c r="G94">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H94">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I94">
         <v>0.5</v>
@@ -5232,7 +5232,7 @@
         <v>누적 가동시간(h)</v>
       </c>
       <c r="E1">
-        <v>390</v>
+        <v>386.5</v>
       </c>
     </row>
     <row r="2">
@@ -5246,13 +5246,13 @@
         <v>누적 Ratio</v>
       </c>
       <c r="D2" t="str">
-        <v>150%</v>
+        <v>148.7%</v>
       </c>
       <c r="E2" t="str">
         <v>누적 아워미터(h)</v>
       </c>
       <c r="F2">
-        <v>1246.5</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="3">
@@ -5272,7 +5272,7 @@
         <v>LPG 합계(kg)</v>
       </c>
       <c r="F3">
-        <v>1451.9</v>
+        <v>1417.9</v>
       </c>
       <c r="G3" t="str">
         <v>요소수 합계(L)</v>
@@ -5298,7 +5298,7 @@
         <v>기본 사이클 합계(회)</v>
       </c>
       <c r="F4">
-        <v>1798</v>
+        <v>1783</v>
       </c>
       <c r="G4" t="str">
         <v>요철 사이클 합계(회)</v>
@@ -5404,7 +5404,7 @@
         <v/>
       </c>
       <c r="O7" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P7" t="str">
         <v>운전자C</v>
@@ -5421,19 +5421,19 @@
         <v>주</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="F8">
-        <v>866.5</v>
+        <v>867</v>
       </c>
       <c r="G8">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H8">
         <v>5</v>
@@ -5448,22 +5448,22 @@
         <v/>
       </c>
       <c r="L8">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="M8">
-        <v>47.1</v>
+        <v>50</v>
       </c>
       <c r="N8" t="str">
         <v/>
       </c>
       <c r="O8" t="str">
-        <v>흐림</v>
+        <v>맑음</v>
       </c>
       <c r="P8" t="str">
         <v>운전자D</v>
       </c>
       <c r="Q8" t="str">
-        <v/>
+        <v>브레이크 페달 유격 커짐(예시)</v>
       </c>
     </row>
     <row r="9">
@@ -5474,19 +5474,19 @@
         <v>주</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="D9">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="E9">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="F9">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="G9">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H9">
         <v>5</v>
@@ -5501,7 +5501,7 @@
         <v/>
       </c>
       <c r="L9">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="M9" t="str">
         <v/>
@@ -5510,7 +5510,7 @@
         <v/>
       </c>
       <c r="O9" t="str">
-        <v>비</v>
+        <v>맑음</v>
       </c>
       <c r="P9" t="str">
         <v>운전자A</v>
@@ -5533,10 +5533,10 @@
         <v>5</v>
       </c>
       <c r="E10">
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
       <c r="F10">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="G10">
         <v>23</v>
@@ -5557,13 +5557,13 @@
         <v>5</v>
       </c>
       <c r="M10">
-        <v>49.3</v>
+        <v>51</v>
       </c>
       <c r="N10" t="str">
         <v/>
       </c>
       <c r="O10" t="str">
-        <v>맑음</v>
+        <v>비</v>
       </c>
       <c r="P10" t="str">
         <v>운전자B</v>
@@ -5580,22 +5580,22 @@
         <v>주</v>
       </c>
       <c r="C11">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="D11">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="E11">
-        <v>27</v>
+        <v>26.5</v>
       </c>
       <c r="F11">
-        <v>883.5</v>
+        <v>883</v>
       </c>
       <c r="G11">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I11">
         <v>0.5</v>
@@ -5607,7 +5607,7 @@
         <v/>
       </c>
       <c r="L11">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="M11" t="str">
         <v/>
@@ -5633,22 +5633,22 @@
         <v>주</v>
       </c>
       <c r="C12">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="D12">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="E12">
-        <v>33.5</v>
+        <v>34</v>
       </c>
       <c r="F12">
-        <v>890</v>
+        <v>890.5</v>
       </c>
       <c r="G12">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I12">
         <v>0.5</v>
@@ -5660,7 +5660,7 @@
         <v/>
       </c>
       <c r="L12">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="M12" t="str">
         <v/>
@@ -5686,10 +5686,10 @@
         <v>주</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="D13">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="E13">
         <v>40.5</v>
@@ -5698,7 +5698,7 @@
         <v>897</v>
       </c>
       <c r="G13">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H13">
         <v>6</v>
@@ -5713,10 +5713,10 @@
         <v/>
       </c>
       <c r="L13">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="M13">
-        <v>58.7</v>
+        <v>54.4</v>
       </c>
       <c r="N13" t="str">
         <v/>
@@ -5739,22 +5739,22 @@
         <v>주</v>
       </c>
       <c r="C14">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D14">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="E14">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F14">
-        <v>902.5</v>
+        <v>903.5</v>
       </c>
       <c r="G14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I14">
         <v>0.5</v>
@@ -5766,7 +5766,7 @@
         <v/>
       </c>
       <c r="L14">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="M14" t="str">
         <v/>
@@ -5775,7 +5775,7 @@
         <v/>
       </c>
       <c r="O14" t="str">
-        <v>맑음</v>
+        <v>비</v>
       </c>
       <c r="P14" t="str">
         <v>운전자B</v>
@@ -5792,22 +5792,22 @@
         <v>주</v>
       </c>
       <c r="C15">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="D15">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="E15">
-        <v>52.5</v>
+        <v>52</v>
       </c>
       <c r="F15">
-        <v>909</v>
+        <v>908.5</v>
       </c>
       <c r="G15">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I15">
         <v>0.5</v>
@@ -5819,7 +5819,7 @@
         <v/>
       </c>
       <c r="L15">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="M15" t="str">
         <v/>
@@ -5828,7 +5828,7 @@
         <v/>
       </c>
       <c r="O15" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P15" t="str">
         <v>운전자D</v>
@@ -5845,10 +5845,10 @@
         <v>주</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="D16">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="E16">
         <v>59.5</v>
@@ -5857,10 +5857,10 @@
         <v>916</v>
       </c>
       <c r="G16">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I16">
         <v>0.5</v>
@@ -5872,7 +5872,7 @@
         <v/>
       </c>
       <c r="L16">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="M16" t="str">
         <v/>
@@ -5898,22 +5898,22 @@
         <v>주</v>
       </c>
       <c r="C17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E17">
-        <v>67.5</v>
+        <v>65.5</v>
       </c>
       <c r="F17">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="G17">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I17">
         <v>0.5</v>
@@ -5925,10 +5925,10 @@
         <v/>
       </c>
       <c r="L17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M17">
-        <v>73.1</v>
+        <v>61.3</v>
       </c>
       <c r="N17" t="str">
         <v/>
@@ -5951,19 +5951,19 @@
         <v>주</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="E18">
-        <v>74.5</v>
+        <v>72</v>
       </c>
       <c r="F18">
-        <v>931</v>
+        <v>928.5</v>
       </c>
       <c r="G18">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H18">
         <v>6</v>
@@ -5978,7 +5978,7 @@
         <v/>
       </c>
       <c r="L18">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="M18" t="str">
         <v/>
@@ -5987,7 +5987,7 @@
         <v/>
       </c>
       <c r="O18" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P18" t="str">
         <v>운전자C</v>
@@ -6004,22 +6004,22 @@
         <v>주</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19">
-        <v>80.5</v>
+        <v>79</v>
       </c>
       <c r="F19">
-        <v>937</v>
+        <v>935.5</v>
       </c>
       <c r="G19">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I19">
         <v>0.5</v>
@@ -6031,22 +6031,22 @@
         <v/>
       </c>
       <c r="L19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M19">
-        <v>55.1</v>
+        <v>60.4</v>
       </c>
       <c r="N19" t="str">
         <v/>
       </c>
       <c r="O19" t="str">
-        <v>비</v>
+        <v>맑음</v>
       </c>
       <c r="P19" t="str">
         <v>운전자D</v>
       </c>
       <c r="Q19" t="str">
-        <v>작동유 온도 경고등 점등 후 소등(예시)</v>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -6057,22 +6057,22 @@
         <v>주</v>
       </c>
       <c r="C20">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="D20">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="E20">
-        <v>87</v>
+        <v>86.5</v>
       </c>
       <c r="F20">
-        <v>943.5</v>
+        <v>943</v>
       </c>
       <c r="G20">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I20">
         <v>0.5</v>
@@ -6084,7 +6084,7 @@
         <v/>
       </c>
       <c r="L20">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="M20" t="str">
         <v/>
@@ -6093,7 +6093,7 @@
         <v/>
       </c>
       <c r="O20" t="str">
-        <v>비</v>
+        <v>흐림</v>
       </c>
       <c r="P20" t="str">
         <v>운전자A</v>
@@ -6110,22 +6110,22 @@
         <v>주</v>
       </c>
       <c r="C21">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="D21">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="E21">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F21">
-        <v>948.5</v>
+        <v>949.5</v>
       </c>
       <c r="G21">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I21">
         <v>0.5</v>
@@ -6137,7 +6137,7 @@
         <v/>
       </c>
       <c r="L21">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="M21" t="str">
         <v/>
@@ -6146,13 +6146,13 @@
         <v/>
       </c>
       <c r="O21" t="str">
-        <v>흐림</v>
+        <v>맑음</v>
       </c>
       <c r="P21" t="str">
         <v>운전자B</v>
       </c>
       <c r="Q21" t="str">
-        <v/>
+        <v>포크 하강 속도 느려짐(예시)</v>
       </c>
     </row>
     <row r="22">
@@ -6163,19 +6163,19 @@
         <v>주</v>
       </c>
       <c r="C22">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="D22">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="E22">
-        <v>99.5</v>
+        <v>101</v>
       </c>
       <c r="F22">
-        <v>956</v>
+        <v>957.5</v>
       </c>
       <c r="G22">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H22">
         <v>7</v>
@@ -6190,10 +6190,10 @@
         <v/>
       </c>
       <c r="L22">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="M22">
-        <v>70.9</v>
+        <v>80.2</v>
       </c>
       <c r="N22" t="str">
         <v/>
@@ -6216,22 +6216,22 @@
         <v>주</v>
       </c>
       <c r="C23">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="E23">
-        <v>107.5</v>
+        <v>106.5</v>
       </c>
       <c r="F23">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="G23">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="H23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I23">
         <v>0.5</v>
@@ -6243,7 +6243,7 @@
         <v/>
       </c>
       <c r="L23">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="M23" t="str">
         <v/>
@@ -6252,7 +6252,7 @@
         <v/>
       </c>
       <c r="O23" t="str">
-        <v>맑음</v>
+        <v>비</v>
       </c>
       <c r="P23" t="str">
         <v>운전자D</v>
@@ -6269,22 +6269,22 @@
         <v>주</v>
       </c>
       <c r="C24">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="D24">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="E24">
-        <v>114</v>
+        <v>111.5</v>
       </c>
       <c r="F24">
-        <v>970.5</v>
+        <v>968</v>
       </c>
       <c r="G24">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I24">
         <v>0.5</v>
@@ -6296,16 +6296,16 @@
         <v/>
       </c>
       <c r="L24">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="M24">
-        <v>55.3</v>
+        <v>45.3</v>
       </c>
       <c r="N24" t="str">
         <v/>
       </c>
       <c r="O24" t="str">
-        <v>흐림</v>
+        <v>맑음</v>
       </c>
       <c r="P24" t="str">
         <v>운전자A</v>
@@ -6322,22 +6322,22 @@
         <v>주</v>
       </c>
       <c r="C25">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="D25">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="E25">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F25">
-        <v>977.5</v>
+        <v>973.5</v>
       </c>
       <c r="G25">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I25">
         <v>0.5</v>
@@ -6349,7 +6349,7 @@
         <v/>
       </c>
       <c r="L25">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="M25" t="str">
         <v/>
@@ -6364,7 +6364,7 @@
         <v>운전자B</v>
       </c>
       <c r="Q25" t="str">
-        <v/>
+        <v>브레이크 페달 유격 커짐(예시)</v>
       </c>
     </row>
     <row r="26">
@@ -6375,22 +6375,22 @@
         <v>주</v>
       </c>
       <c r="C26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E26">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="F26">
-        <v>984.5</v>
+        <v>978.5</v>
       </c>
       <c r="G26">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I26">
         <v>0.5</v>
@@ -6402,7 +6402,7 @@
         <v/>
       </c>
       <c r="L26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M26" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v/>
       </c>
       <c r="O26" t="str">
-        <v>비</v>
+        <v>맑음</v>
       </c>
       <c r="P26" t="str">
         <v>운전자C</v>
@@ -6428,22 +6428,22 @@
         <v>주</v>
       </c>
       <c r="C27">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="D27">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="E27">
-        <v>134.5</v>
+        <v>127</v>
       </c>
       <c r="F27">
-        <v>991</v>
+        <v>983.5</v>
       </c>
       <c r="G27">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I27">
         <v>0.5</v>
@@ -6455,22 +6455,22 @@
         <v/>
       </c>
       <c r="L27">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="M27">
-        <v>60.5</v>
+        <v>50.9</v>
       </c>
       <c r="N27" t="str">
         <v/>
       </c>
       <c r="O27" t="str">
-        <v>흐림</v>
+        <v>비</v>
       </c>
       <c r="P27" t="str">
         <v>운전자D</v>
       </c>
       <c r="Q27" t="str">
-        <v>포크 하강 속도 느려짐(예시)</v>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -6481,19 +6481,19 @@
         <v>주</v>
       </c>
       <c r="C28">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="D28">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="E28">
-        <v>142.5</v>
+        <v>134.5</v>
       </c>
       <c r="F28">
-        <v>999</v>
+        <v>991</v>
       </c>
       <c r="G28">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H28">
         <v>7</v>
@@ -6508,16 +6508,16 @@
         <v/>
       </c>
       <c r="L28">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="M28">
-        <v>80.2</v>
+        <v>68.4</v>
       </c>
       <c r="N28" t="str">
         <v/>
       </c>
       <c r="O28" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P28" t="str">
         <v>운전자B</v>
@@ -6534,19 +6534,19 @@
         <v>주</v>
       </c>
       <c r="C29">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="D29">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="E29">
-        <v>148</v>
+        <v>139.5</v>
       </c>
       <c r="F29">
-        <v>1004.5</v>
+        <v>996</v>
       </c>
       <c r="G29">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H29">
         <v>5</v>
@@ -6561,7 +6561,7 @@
         <v/>
       </c>
       <c r="L29">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="M29" t="str">
         <v/>
@@ -6570,7 +6570,7 @@
         <v/>
       </c>
       <c r="O29" t="str">
-        <v>비</v>
+        <v>맑음</v>
       </c>
       <c r="P29" t="str">
         <v>운전자C</v>
@@ -6587,22 +6587,22 @@
         <v>주</v>
       </c>
       <c r="C30">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E30">
-        <v>153</v>
+        <v>147.5</v>
       </c>
       <c r="F30">
-        <v>1009.5</v>
+        <v>1004</v>
       </c>
       <c r="G30">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="H30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I30">
         <v>0.5</v>
@@ -6614,7 +6614,7 @@
         <v/>
       </c>
       <c r="L30">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M30" t="str">
         <v/>
@@ -6623,7 +6623,7 @@
         <v/>
       </c>
       <c r="O30" t="str">
-        <v>맑음</v>
+        <v>비</v>
       </c>
       <c r="P30" t="str">
         <v>운전자D</v>
@@ -6640,19 +6640,19 @@
         <v>주</v>
       </c>
       <c r="C31">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="D31">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="E31">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="F31">
-        <v>1015.5</v>
+        <v>1009.5</v>
       </c>
       <c r="G31">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H31">
         <v>5</v>
@@ -6667,22 +6667,22 @@
         <v/>
       </c>
       <c r="L31">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="M31">
-        <v>51.8</v>
+        <v>48.7</v>
       </c>
       <c r="N31" t="str">
         <v/>
       </c>
       <c r="O31" t="str">
-        <v>흐림</v>
+        <v>비</v>
       </c>
       <c r="P31" t="str">
         <v>운전자A</v>
       </c>
       <c r="Q31" t="str">
-        <v>브레이크 페달 유격 커짐(예시)</v>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -6699,10 +6699,10 @@
         <v>5</v>
       </c>
       <c r="E32">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="F32">
-        <v>1020.5</v>
+        <v>1014.5</v>
       </c>
       <c r="G32">
         <v>23</v>
@@ -6746,22 +6746,22 @@
         <v>주</v>
       </c>
       <c r="C33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E33">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F33">
-        <v>1025.5</v>
+        <v>1021.5</v>
       </c>
       <c r="G33">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I33">
         <v>0.5</v>
@@ -6773,22 +6773,22 @@
         <v/>
       </c>
       <c r="L33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M33">
-        <v>50.9</v>
+        <v>69.3</v>
       </c>
       <c r="N33" t="str">
         <v/>
       </c>
       <c r="O33" t="str">
-        <v>비</v>
+        <v>맑음</v>
       </c>
       <c r="P33" t="str">
         <v>운전자C</v>
       </c>
       <c r="Q33" t="str">
-        <v/>
+        <v>브레이크 페달 유격 커짐(예시)</v>
       </c>
     </row>
     <row r="34">
@@ -6799,22 +6799,22 @@
         <v>주</v>
       </c>
       <c r="C34">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="D34">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="E34">
-        <v>176.5</v>
+        <v>170</v>
       </c>
       <c r="F34">
-        <v>1033</v>
+        <v>1026.5</v>
       </c>
       <c r="G34">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I34">
         <v>0.5</v>
@@ -6826,7 +6826,7 @@
         <v/>
       </c>
       <c r="L34">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="M34" t="str">
         <v/>
@@ -6835,7 +6835,7 @@
         <v/>
       </c>
       <c r="O34" t="str">
-        <v>흐림</v>
+        <v>맑음</v>
       </c>
       <c r="P34" t="str">
         <v>운전자D</v>
@@ -6852,19 +6852,19 @@
         <v>주</v>
       </c>
       <c r="C35">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="D35">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="E35">
-        <v>182.5</v>
+        <v>175.5</v>
       </c>
       <c r="F35">
-        <v>1039</v>
+        <v>1032</v>
       </c>
       <c r="G35">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H35">
         <v>5</v>
@@ -6879,7 +6879,7 @@
         <v/>
       </c>
       <c r="L35">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="M35" t="str">
         <v/>
@@ -6888,13 +6888,13 @@
         <v/>
       </c>
       <c r="O35" t="str">
-        <v>흐림</v>
+        <v>맑음</v>
       </c>
       <c r="P35" t="str">
         <v>운전자A</v>
       </c>
       <c r="Q35" t="str">
-        <v>충전 커넥터 체결 불량(예시)</v>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -6905,22 +6905,22 @@
         <v>주</v>
       </c>
       <c r="C36">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="D36">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="E36">
-        <v>190.5</v>
+        <v>182</v>
       </c>
       <c r="F36">
-        <v>1047</v>
+        <v>1038.5</v>
       </c>
       <c r="G36">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I36">
         <v>0.5</v>
@@ -6932,16 +6932,16 @@
         <v/>
       </c>
       <c r="L36">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="M36">
-        <v>74.6</v>
+        <v>57</v>
       </c>
       <c r="N36" t="str">
         <v/>
       </c>
       <c r="O36" t="str">
-        <v>비</v>
+        <v>흐림</v>
       </c>
       <c r="P36" t="str">
         <v>운전자B</v>
@@ -6958,22 +6958,22 @@
         <v>주</v>
       </c>
       <c r="C37">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="D37">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="E37">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="F37">
-        <v>1052.5</v>
+        <v>1045.5</v>
       </c>
       <c r="G37">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I37">
         <v>0.5</v>
@@ -6985,7 +6985,7 @@
         <v/>
       </c>
       <c r="L37">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="M37" t="str">
         <v/>
@@ -6994,7 +6994,7 @@
         <v/>
       </c>
       <c r="O37" t="str">
-        <v>맑음</v>
+        <v>비</v>
       </c>
       <c r="P37" t="str">
         <v>운전자C</v>
@@ -7011,19 +7011,19 @@
         <v>주</v>
       </c>
       <c r="C38">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="D38">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="E38">
-        <v>201</v>
+        <v>194.5</v>
       </c>
       <c r="F38">
-        <v>1057.5</v>
+        <v>1051</v>
       </c>
       <c r="G38">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H38">
         <v>5</v>
@@ -7038,22 +7038,22 @@
         <v/>
       </c>
       <c r="L38">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="M38">
-        <v>47.4</v>
+        <v>50.6</v>
       </c>
       <c r="N38" t="str">
         <v/>
       </c>
       <c r="O38" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P38" t="str">
         <v>운전자D</v>
       </c>
       <c r="Q38" t="str">
-        <v>브레이크 페달 유격 커짐(예시)</v>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -7064,22 +7064,22 @@
         <v>주</v>
       </c>
       <c r="C39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E39">
-        <v>206</v>
+        <v>201.5</v>
       </c>
       <c r="F39">
-        <v>1062.5</v>
+        <v>1058</v>
       </c>
       <c r="G39">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I39">
         <v>0.5</v>
@@ -7091,7 +7091,7 @@
         <v/>
       </c>
       <c r="L39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M39" t="str">
         <v/>
@@ -7100,7 +7100,7 @@
         <v/>
       </c>
       <c r="O39" t="str">
-        <v>비</v>
+        <v>맑음</v>
       </c>
       <c r="P39" t="str">
         <v>운전자A</v>
@@ -7117,22 +7117,22 @@
         <v>주</v>
       </c>
       <c r="C40">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D40">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E40">
-        <v>211</v>
+        <v>209.5</v>
       </c>
       <c r="F40">
-        <v>1067.5</v>
+        <v>1066</v>
       </c>
       <c r="G40">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="H40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I40">
         <v>0.5</v>
@@ -7144,7 +7144,7 @@
         <v/>
       </c>
       <c r="L40">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M40" t="str">
         <v/>
@@ -7153,7 +7153,7 @@
         <v/>
       </c>
       <c r="O40" t="str">
-        <v>맑음</v>
+        <v>비</v>
       </c>
       <c r="P40" t="str">
         <v>운전자B</v>
@@ -7170,22 +7170,22 @@
         <v>주</v>
       </c>
       <c r="C41">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D41">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="E41">
-        <v>216.5</v>
+        <v>216</v>
       </c>
       <c r="F41">
-        <v>1073</v>
+        <v>1072.5</v>
       </c>
       <c r="G41">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I41">
         <v>0.5</v>
@@ -7197,16 +7197,16 @@
         <v/>
       </c>
       <c r="L41">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="M41">
-        <v>54</v>
+        <v>66.4</v>
       </c>
       <c r="N41" t="str">
         <v/>
       </c>
       <c r="O41" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P41" t="str">
         <v>운전자C</v>
@@ -7223,22 +7223,22 @@
         <v>주</v>
       </c>
       <c r="C42">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="D42">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="E42">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F42">
-        <v>1078.5</v>
+        <v>1079.5</v>
       </c>
       <c r="G42">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I42">
         <v>0.5</v>
@@ -7250,7 +7250,7 @@
         <v/>
       </c>
       <c r="L42">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="M42" t="str">
         <v/>
@@ -7259,7 +7259,7 @@
         <v/>
       </c>
       <c r="O42" t="str">
-        <v>맑음</v>
+        <v>비</v>
       </c>
       <c r="P42" t="str">
         <v>운전자D</v>
@@ -7276,22 +7276,22 @@
         <v>주</v>
       </c>
       <c r="C43">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="D43">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="E43">
-        <v>229</v>
+        <v>230.5</v>
       </c>
       <c r="F43">
-        <v>1085.5</v>
+        <v>1087</v>
       </c>
       <c r="G43">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I43">
         <v>0.5</v>
@@ -7303,16 +7303,16 @@
         <v/>
       </c>
       <c r="L43">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="M43">
-        <v>64.2</v>
+        <v>63.7</v>
       </c>
       <c r="N43" t="str">
         <v/>
       </c>
       <c r="O43" t="str">
-        <v>비</v>
+        <v>맑음</v>
       </c>
       <c r="P43" t="str">
         <v>운전자A</v>
@@ -7329,10 +7329,10 @@
         <v>주</v>
       </c>
       <c r="C44">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="D44">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="E44">
         <v>235.5</v>
@@ -7341,10 +7341,10 @@
         <v>1092</v>
       </c>
       <c r="G44">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I44">
         <v>0.5</v>
@@ -7356,7 +7356,7 @@
         <v/>
       </c>
       <c r="L44">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="M44" t="str">
         <v/>
@@ -7365,7 +7365,7 @@
         <v/>
       </c>
       <c r="O44" t="str">
-        <v>맑음</v>
+        <v>비</v>
       </c>
       <c r="P44" t="str">
         <v>운전자B</v>
@@ -7382,22 +7382,22 @@
         <v>주</v>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E45">
-        <v>242.5</v>
+        <v>241.5</v>
       </c>
       <c r="F45">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="G45">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I45">
         <v>0.5</v>
@@ -7409,7 +7409,7 @@
         <v/>
       </c>
       <c r="L45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M45" t="str">
         <v/>
@@ -7418,7 +7418,7 @@
         <v/>
       </c>
       <c r="O45" t="str">
-        <v>맑음</v>
+        <v>비</v>
       </c>
       <c r="P45" t="str">
         <v>운전자C</v>
@@ -7441,10 +7441,10 @@
         <v>8</v>
       </c>
       <c r="E46">
-        <v>250.5</v>
+        <v>249.5</v>
       </c>
       <c r="F46">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="G46">
         <v>37</v>
@@ -7465,13 +7465,13 @@
         <v>8</v>
       </c>
       <c r="M46">
-        <v>77</v>
+        <v>74.7</v>
       </c>
       <c r="N46" t="str">
         <v/>
       </c>
       <c r="O46" t="str">
-        <v>비</v>
+        <v>흐림</v>
       </c>
       <c r="P46" t="str">
         <v>운전자D</v>
@@ -7488,19 +7488,19 @@
         <v>주</v>
       </c>
       <c r="C47">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="D47">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="E47">
-        <v>258.5</v>
+        <v>257</v>
       </c>
       <c r="F47">
-        <v>1115</v>
+        <v>1113.5</v>
       </c>
       <c r="G47">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H47">
         <v>7</v>
@@ -7515,7 +7515,7 @@
         <v/>
       </c>
       <c r="L47">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="M47" t="str">
         <v/>
@@ -7541,22 +7541,22 @@
         <v>주</v>
       </c>
       <c r="C48">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="D48">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="E48">
-        <v>265.5</v>
+        <v>264.5</v>
       </c>
       <c r="F48">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G48">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H48">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I48">
         <v>0.5</v>
@@ -7568,16 +7568,16 @@
         <v/>
       </c>
       <c r="L48">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="M48">
-        <v>67.3</v>
+        <v>76.1</v>
       </c>
       <c r="N48" t="str">
         <v/>
       </c>
       <c r="O48" t="str">
-        <v>비</v>
+        <v>맑음</v>
       </c>
       <c r="P48" t="str">
         <v>운전자B</v>
@@ -7594,22 +7594,22 @@
         <v>주</v>
       </c>
       <c r="C49">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E49">
-        <v>270.5</v>
+        <v>272.5</v>
       </c>
       <c r="F49">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="G49">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="H49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I49">
         <v>0.5</v>
@@ -7630,7 +7630,7 @@
         <v/>
       </c>
       <c r="O49" t="str">
-        <v>비</v>
+        <v>맑음</v>
       </c>
       <c r="P49" t="str">
         <v>운전자C</v>
@@ -7647,22 +7647,22 @@
         <v>주</v>
       </c>
       <c r="C50">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="D50">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="E50">
-        <v>275.5</v>
+        <v>280</v>
       </c>
       <c r="F50">
-        <v>1132</v>
+        <v>1136.5</v>
       </c>
       <c r="G50">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H50">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I50">
         <v>0.5</v>
@@ -7683,7 +7683,7 @@
         <v/>
       </c>
       <c r="O50" t="str">
-        <v>비</v>
+        <v>맑음</v>
       </c>
       <c r="P50" t="str">
         <v>운전자D</v>
@@ -7700,19 +7700,19 @@
         <v>주</v>
       </c>
       <c r="C51">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D51">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E51">
-        <v>281.5</v>
+        <v>285</v>
       </c>
       <c r="F51">
-        <v>1138</v>
+        <v>1141.5</v>
       </c>
       <c r="G51">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H51">
         <v>5</v>
@@ -7730,13 +7730,13 @@
         <v/>
       </c>
       <c r="M51">
-        <v>57</v>
+        <v>50.4</v>
       </c>
       <c r="N51" t="str">
         <v/>
       </c>
       <c r="O51" t="str">
-        <v>비</v>
+        <v>맑음</v>
       </c>
       <c r="P51" t="str">
         <v>운전자A</v>
@@ -7753,22 +7753,22 @@
         <v>주</v>
       </c>
       <c r="C52">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="D52">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="E52">
-        <v>288</v>
+        <v>292.5</v>
       </c>
       <c r="F52">
-        <v>1144.5</v>
+        <v>1149</v>
       </c>
       <c r="G52">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H52">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I52">
         <v>0.5</v>
@@ -7789,7 +7789,7 @@
         <v/>
       </c>
       <c r="O52" t="str">
-        <v>비</v>
+        <v>맑음</v>
       </c>
       <c r="P52" t="str">
         <v>운전자B</v>
@@ -7806,22 +7806,22 @@
         <v>주</v>
       </c>
       <c r="C53">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="D53">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="E53">
-        <v>295.5</v>
+        <v>299</v>
       </c>
       <c r="F53">
-        <v>1152</v>
+        <v>1155.5</v>
       </c>
       <c r="G53">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H53">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I53">
         <v>0.5</v>
@@ -7836,7 +7836,7 @@
         <v/>
       </c>
       <c r="M53">
-        <v>68.1</v>
+        <v>57.6</v>
       </c>
       <c r="N53" t="str">
         <v/>
@@ -7859,22 +7859,22 @@
         <v>주</v>
       </c>
       <c r="C54">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D54">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E54">
-        <v>303.5</v>
+        <v>305</v>
       </c>
       <c r="F54">
-        <v>1160</v>
+        <v>1161.5</v>
       </c>
       <c r="G54">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H54">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I54">
         <v>0.5</v>
@@ -7895,7 +7895,7 @@
         <v/>
       </c>
       <c r="O54" t="str">
-        <v>흐림</v>
+        <v>맑음</v>
       </c>
       <c r="P54" t="str">
         <v>운전자D</v>
@@ -7912,10 +7912,10 @@
         <v>주</v>
       </c>
       <c r="C55">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="D55">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="E55">
         <v>311.5</v>
@@ -7924,10 +7924,10 @@
         <v>1168</v>
       </c>
       <c r="G55">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H55">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I55">
         <v>0.5</v>
@@ -7954,7 +7954,7 @@
         <v>운전자A</v>
       </c>
       <c r="Q55" t="str">
-        <v/>
+        <v>브레이크 페달 유격 커짐(예시)</v>
       </c>
     </row>
     <row r="56">
@@ -7965,22 +7965,22 @@
         <v>주</v>
       </c>
       <c r="C56">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="D56">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="E56">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F56">
-        <v>1175.5</v>
+        <v>1174.5</v>
       </c>
       <c r="G56">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I56">
         <v>0.5</v>
@@ -7995,7 +7995,7 @@
         <v/>
       </c>
       <c r="M56">
-        <v>67</v>
+        <v>65.6</v>
       </c>
       <c r="N56" t="str">
         <v/>
@@ -8018,19 +8018,19 @@
         <v>주</v>
       </c>
       <c r="C57">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="D57">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="E57">
-        <v>327</v>
+        <v>325.5</v>
       </c>
       <c r="F57">
-        <v>1183.5</v>
+        <v>1182</v>
       </c>
       <c r="G57">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H57">
         <v>7</v>
@@ -8071,22 +8071,22 @@
         <v>주</v>
       </c>
       <c r="C58">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="D58">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="E58">
-        <v>334.5</v>
+        <v>332.5</v>
       </c>
       <c r="F58">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="G58">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H58">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I58">
         <v>0.5</v>
@@ -8101,7 +8101,7 @@
         <v/>
       </c>
       <c r="M58">
-        <v>65.6</v>
+        <v>61.4</v>
       </c>
       <c r="N58" t="str">
         <v/>
@@ -8124,22 +8124,22 @@
         <v>주</v>
       </c>
       <c r="C59">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D59">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="E59">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F59">
-        <v>1196.5</v>
+        <v>1195.5</v>
       </c>
       <c r="G59">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H59">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I59">
         <v>0.5</v>
@@ -8160,7 +8160,7 @@
         <v/>
       </c>
       <c r="O59" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P59" t="str">
         <v>운전자A</v>
@@ -8177,19 +8177,19 @@
         <v>주</v>
       </c>
       <c r="C60">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D60">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E60">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F60">
-        <v>1202.5</v>
+        <v>1200.5</v>
       </c>
       <c r="G60">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H60">
         <v>5</v>
@@ -8219,7 +8219,7 @@
         <v>운전자B</v>
       </c>
       <c r="Q60" t="str">
-        <v/>
+        <v>작동유 온도 경고등 점등 후 소등(예시)</v>
       </c>
     </row>
     <row r="61">
@@ -8230,22 +8230,22 @@
         <v>주</v>
       </c>
       <c r="C61">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D61">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="E61">
-        <v>352.5</v>
+        <v>349.5</v>
       </c>
       <c r="F61">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="G61">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H61">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I61">
         <v>0.5</v>
@@ -8260,7 +8260,7 @@
         <v/>
       </c>
       <c r="M61">
-        <v>55.5</v>
+        <v>47.5</v>
       </c>
       <c r="N61" t="str">
         <v/>
@@ -8283,22 +8283,22 @@
         <v>주</v>
       </c>
       <c r="C62">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="D62">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="E62">
-        <v>359</v>
+        <v>357.5</v>
       </c>
       <c r="F62">
-        <v>1215.5</v>
+        <v>1214</v>
       </c>
       <c r="G62">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H62">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I62">
         <v>0.5</v>
@@ -8319,13 +8319,13 @@
         <v/>
       </c>
       <c r="O62" t="str">
-        <v>맑음</v>
+        <v>비</v>
       </c>
       <c r="P62" t="str">
         <v>운전자D</v>
       </c>
       <c r="Q62" t="str">
-        <v/>
+        <v>포크 하강 속도 느려짐(예시)</v>
       </c>
     </row>
     <row r="63">
@@ -8342,10 +8342,10 @@
         <v>6</v>
       </c>
       <c r="E63">
-        <v>365</v>
+        <v>363.5</v>
       </c>
       <c r="F63">
-        <v>1221.5</v>
+        <v>1220</v>
       </c>
       <c r="G63">
         <v>28</v>
@@ -8366,13 +8366,13 @@
         <v/>
       </c>
       <c r="M63">
-        <v>58.5</v>
+        <v>55.9</v>
       </c>
       <c r="N63" t="str">
         <v/>
       </c>
       <c r="O63" t="str">
-        <v>비</v>
+        <v>맑음</v>
       </c>
       <c r="P63" t="str">
         <v>운전자A</v>
@@ -8389,22 +8389,22 @@
         <v>주</v>
       </c>
       <c r="C64">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="D64">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="E64">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="F64">
-        <v>1228.5</v>
+        <v>1225.5</v>
       </c>
       <c r="G64">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H64">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I64">
         <v>0.5</v>
@@ -8442,22 +8442,22 @@
         <v>주</v>
       </c>
       <c r="C65">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="D65">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="E65">
-        <v>379.5</v>
+        <v>375.5</v>
       </c>
       <c r="F65">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="G65">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H65">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I65">
         <v>0.5</v>
@@ -8495,19 +8495,19 @@
         <v>주</v>
       </c>
       <c r="C66">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="D66">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="E66">
-        <v>384.5</v>
+        <v>381</v>
       </c>
       <c r="F66">
-        <v>1241</v>
+        <v>1237.5</v>
       </c>
       <c r="G66">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H66">
         <v>5</v>
@@ -8525,19 +8525,19 @@
         <v/>
       </c>
       <c r="M66">
-        <v>42.8</v>
+        <v>51.1</v>
       </c>
       <c r="N66" t="str">
         <v/>
       </c>
       <c r="O66" t="str">
-        <v>흐림</v>
+        <v>맑음</v>
       </c>
       <c r="P66" t="str">
         <v>운전자D</v>
       </c>
       <c r="Q66" t="str">
-        <v>작동유 온도 경고등 점등 후 소등(예시)</v>
+        <v>좌측 마스트 체인에서 소음 발생(예시)</v>
       </c>
     </row>
     <row r="67">
@@ -8554,10 +8554,10 @@
         <v>5.5</v>
       </c>
       <c r="E67">
-        <v>390</v>
+        <v>386.5</v>
       </c>
       <c r="F67">
-        <v>1246.5</v>
+        <v>1243</v>
       </c>
       <c r="G67">
         <v>25</v>
@@ -8618,7 +8618,7 @@
         <v>누적 가동시간(h)</v>
       </c>
       <c r="E1">
-        <v>415.5</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2">
@@ -8632,13 +8632,13 @@
         <v>누적 Ratio</v>
       </c>
       <c r="D2" t="str">
-        <v>83.1%</v>
+        <v>80.6%</v>
       </c>
       <c r="E2" t="str">
         <v>누적 아워미터(h)</v>
       </c>
       <c r="F2">
-        <v>847.5</v>
+        <v>835</v>
       </c>
     </row>
     <row r="3">
@@ -8652,7 +8652,7 @@
         <v>남은 시간(h)</v>
       </c>
       <c r="D3">
-        <v>84.5</v>
+        <v>97</v>
       </c>
       <c r="E3" t="str">
         <v>경유 합계(L)</v>
@@ -8684,13 +8684,13 @@
         <v>기본 사이클 합계(회)</v>
       </c>
       <c r="F4">
-        <v>1918</v>
+        <v>1860</v>
       </c>
       <c r="G4" t="str">
         <v>요철 사이클 합계(회)</v>
       </c>
       <c r="H4">
-        <v>373</v>
+        <v>364</v>
       </c>
     </row>
     <row r="6">
@@ -8754,19 +8754,19 @@
         <v>주</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="F7">
-        <v>440</v>
+        <v>439.5</v>
       </c>
       <c r="G7">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H7">
         <v>7</v>
@@ -8781,7 +8781,7 @@
         <v/>
       </c>
       <c r="L7">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="M7" t="str">
         <v/>
@@ -8796,7 +8796,7 @@
         <v>운전자D</v>
       </c>
       <c r="Q7" t="str">
-        <v>포크 하강 속도 느려짐(예시)</v>
+        <v>운전석 계기판 화면 깜빡임(예시)</v>
       </c>
     </row>
     <row r="8">
@@ -8807,19 +8807,19 @@
         <v>주</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="F8">
-        <v>446</v>
+        <v>444.5</v>
       </c>
       <c r="G8">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H8">
         <v>5</v>
@@ -8834,7 +8834,7 @@
         <v/>
       </c>
       <c r="L8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M8" t="str">
         <v/>
@@ -8843,7 +8843,7 @@
         <v/>
       </c>
       <c r="O8" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P8" t="str">
         <v>운전자A</v>
@@ -8860,22 +8860,22 @@
         <v>주</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="D9">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="E9">
-        <v>19.5</v>
+        <v>20.5</v>
       </c>
       <c r="F9">
-        <v>451.5</v>
+        <v>452.5</v>
       </c>
       <c r="G9">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="H9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I9">
         <v>0.5</v>
@@ -8887,7 +8887,7 @@
         <v/>
       </c>
       <c r="L9">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="M9" t="str">
         <v/>
@@ -8919,10 +8919,10 @@
         <v>6.5</v>
       </c>
       <c r="E10">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F10">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G10">
         <v>30</v>
@@ -8966,22 +8966,22 @@
         <v>주</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="E11">
-        <v>31</v>
+        <v>33.5</v>
       </c>
       <c r="F11">
-        <v>463</v>
+        <v>465.5</v>
       </c>
       <c r="G11">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I11">
         <v>0.5</v>
@@ -8993,7 +8993,7 @@
         <v/>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="M11" t="str">
         <v/>
@@ -9025,10 +9025,10 @@
         <v>6</v>
       </c>
       <c r="E12">
-        <v>37</v>
+        <v>39.5</v>
       </c>
       <c r="F12">
-        <v>469</v>
+        <v>471.5</v>
       </c>
       <c r="G12">
         <v>28</v>
@@ -9072,22 +9072,22 @@
         <v>주</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D13">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E13">
-        <v>42</v>
+        <v>47.5</v>
       </c>
       <c r="F13">
-        <v>474</v>
+        <v>479.5</v>
       </c>
       <c r="G13">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="H13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I13">
         <v>0.5</v>
@@ -9099,7 +9099,7 @@
         <v/>
       </c>
       <c r="L13">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M13" t="str">
         <v/>
@@ -9108,7 +9108,7 @@
         <v/>
       </c>
       <c r="O13" t="str">
-        <v>비</v>
+        <v>맑음</v>
       </c>
       <c r="P13" t="str">
         <v>운전자B</v>
@@ -9125,22 +9125,22 @@
         <v>주</v>
       </c>
       <c r="C14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E14">
-        <v>50</v>
+        <v>52.5</v>
       </c>
       <c r="F14">
-        <v>482</v>
+        <v>484.5</v>
       </c>
       <c r="G14">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="H14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I14">
         <v>0.5</v>
@@ -9152,7 +9152,7 @@
         <v/>
       </c>
       <c r="L14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M14" t="str">
         <v/>
@@ -9161,7 +9161,7 @@
         <v/>
       </c>
       <c r="O14" t="str">
-        <v>맑음</v>
+        <v>비</v>
       </c>
       <c r="P14" t="str">
         <v>운전자C</v>
@@ -9178,22 +9178,22 @@
         <v>주</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E15">
-        <v>57</v>
+        <v>57.5</v>
       </c>
       <c r="F15">
-        <v>489</v>
+        <v>489.5</v>
       </c>
       <c r="G15">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I15">
         <v>0.5</v>
@@ -9205,7 +9205,7 @@
         <v/>
       </c>
       <c r="L15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M15" t="str">
         <v/>
@@ -9231,22 +9231,22 @@
         <v>주</v>
       </c>
       <c r="C16">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="D16">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="E16">
-        <v>64.5</v>
+        <v>64</v>
       </c>
       <c r="F16">
-        <v>496.5</v>
+        <v>496</v>
       </c>
       <c r="G16">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I16">
         <v>0.5</v>
@@ -9258,7 +9258,7 @@
         <v/>
       </c>
       <c r="L16">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="M16" t="str">
         <v/>
@@ -9267,7 +9267,7 @@
         <v/>
       </c>
       <c r="O16" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P16" t="str">
         <v>운전자A</v>
@@ -9290,10 +9290,10 @@
         <v>6.5</v>
       </c>
       <c r="E17">
-        <v>71</v>
+        <v>70.5</v>
       </c>
       <c r="F17">
-        <v>503</v>
+        <v>502.5</v>
       </c>
       <c r="G17">
         <v>30</v>
@@ -9337,22 +9337,22 @@
         <v>주</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E18">
-        <v>78</v>
+        <v>76.5</v>
       </c>
       <c r="F18">
-        <v>510</v>
+        <v>508.5</v>
       </c>
       <c r="G18">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I18">
         <v>0.5</v>
@@ -9364,7 +9364,7 @@
         <v/>
       </c>
       <c r="L18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M18" t="str">
         <v/>
@@ -9373,7 +9373,7 @@
         <v/>
       </c>
       <c r="O18" t="str">
-        <v>맑음</v>
+        <v>비</v>
       </c>
       <c r="P18" t="str">
         <v>운전자C</v>
@@ -9390,22 +9390,22 @@
         <v>주</v>
       </c>
       <c r="C19">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="D19">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="E19">
-        <v>84.5</v>
+        <v>81.5</v>
       </c>
       <c r="F19">
-        <v>516.5</v>
+        <v>513.5</v>
       </c>
       <c r="G19">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I19">
         <v>0.5</v>
@@ -9417,7 +9417,7 @@
         <v/>
       </c>
       <c r="L19">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="M19" t="str">
         <v/>
@@ -9426,7 +9426,7 @@
         <v/>
       </c>
       <c r="O19" t="str">
-        <v>비</v>
+        <v>맑음</v>
       </c>
       <c r="P19" t="str">
         <v>운전자D</v>
@@ -9443,22 +9443,22 @@
         <v>주</v>
       </c>
       <c r="C20">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D20">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E20">
-        <v>92.5</v>
+        <v>87.5</v>
       </c>
       <c r="F20">
-        <v>524.5</v>
+        <v>519.5</v>
       </c>
       <c r="G20">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I20">
         <v>0.5</v>
@@ -9470,7 +9470,7 @@
         <v/>
       </c>
       <c r="L20">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M20" t="str">
         <v/>
@@ -9479,7 +9479,7 @@
         <v/>
       </c>
       <c r="O20" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P20" t="str">
         <v>운전자A</v>
@@ -9496,22 +9496,22 @@
         <v>주</v>
       </c>
       <c r="C21">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="D21">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="E21">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="F21">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="G21">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I21">
         <v>0.5</v>
@@ -9523,7 +9523,7 @@
         <v/>
       </c>
       <c r="L21">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="M21" t="str">
         <v/>
@@ -9532,7 +9532,7 @@
         <v/>
       </c>
       <c r="O21" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P21" t="str">
         <v>운전자B</v>
@@ -9555,10 +9555,10 @@
         <v>7.5</v>
       </c>
       <c r="E22">
-        <v>107.5</v>
+        <v>100.5</v>
       </c>
       <c r="F22">
-        <v>539.5</v>
+        <v>532.5</v>
       </c>
       <c r="G22">
         <v>35</v>
@@ -9591,7 +9591,7 @@
         <v>운전자C</v>
       </c>
       <c r="Q22" t="str">
-        <v/>
+        <v>작동유 온도 경고등 점등 후 소등(예시)</v>
       </c>
     </row>
     <row r="23">
@@ -9602,22 +9602,22 @@
         <v>주</v>
       </c>
       <c r="C23">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E23">
-        <v>115.5</v>
+        <v>106.5</v>
       </c>
       <c r="F23">
-        <v>547.5</v>
+        <v>538.5</v>
       </c>
       <c r="G23">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I23">
         <v>0.5</v>
@@ -9629,7 +9629,7 @@
         <v/>
       </c>
       <c r="L23">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M23" t="str">
         <v/>
@@ -9655,19 +9655,19 @@
         <v>주</v>
       </c>
       <c r="C24">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="D24">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="E24">
-        <v>122.5</v>
+        <v>113</v>
       </c>
       <c r="F24">
-        <v>554.5</v>
+        <v>545</v>
       </c>
       <c r="G24">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H24">
         <v>6</v>
@@ -9682,7 +9682,7 @@
         <v/>
       </c>
       <c r="L24">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="M24" t="str">
         <v/>
@@ -9708,22 +9708,22 @@
         <v>주</v>
       </c>
       <c r="C25">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="D25">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="E25">
-        <v>129</v>
+        <v>120.5</v>
       </c>
       <c r="F25">
-        <v>561</v>
+        <v>552.5</v>
       </c>
       <c r="G25">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I25">
         <v>0.5</v>
@@ -9735,7 +9735,7 @@
         <v/>
       </c>
       <c r="L25">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="M25" t="str">
         <v/>
@@ -9750,7 +9750,7 @@
         <v>운전자B</v>
       </c>
       <c r="Q25" t="str">
-        <v/>
+        <v>작동유 온도 경고등 점등 후 소등(예시)</v>
       </c>
     </row>
     <row r="26">
@@ -9761,22 +9761,22 @@
         <v>주</v>
       </c>
       <c r="C26">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="D26">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="E26">
-        <v>135.5</v>
+        <v>128.5</v>
       </c>
       <c r="F26">
-        <v>567.5</v>
+        <v>560.5</v>
       </c>
       <c r="G26">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I26">
         <v>0.5</v>
@@ -9788,7 +9788,7 @@
         <v/>
       </c>
       <c r="L26">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="M26" t="str">
         <v/>
@@ -9814,19 +9814,19 @@
         <v>주</v>
       </c>
       <c r="C27">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="D27">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="E27">
-        <v>141.5</v>
+        <v>134</v>
       </c>
       <c r="F27">
-        <v>573.5</v>
+        <v>566</v>
       </c>
       <c r="G27">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H27">
         <v>5</v>
@@ -9841,7 +9841,7 @@
         <v/>
       </c>
       <c r="L27">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="M27" t="str">
         <v/>
@@ -9867,22 +9867,22 @@
         <v>주</v>
       </c>
       <c r="C28">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="D28">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="E28">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="F28">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="G28">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I28">
         <v>0.5</v>
@@ -9894,7 +9894,7 @@
         <v/>
       </c>
       <c r="L28">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="M28" t="str">
         <v/>
@@ -9903,7 +9903,7 @@
         <v/>
       </c>
       <c r="O28" t="str">
-        <v>비</v>
+        <v>맑음</v>
       </c>
       <c r="P28" t="str">
         <v>운전자A</v>
@@ -9920,22 +9920,22 @@
         <v>주</v>
       </c>
       <c r="C29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E29">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="F29">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="G29">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="H29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I29">
         <v>0.5</v>
@@ -9947,7 +9947,7 @@
         <v/>
       </c>
       <c r="L29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M29" t="str">
         <v/>
@@ -9973,19 +9973,19 @@
         <v>주</v>
       </c>
       <c r="C30">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="D30">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="E30">
-        <v>161.5</v>
+        <v>156</v>
       </c>
       <c r="F30">
-        <v>593.5</v>
+        <v>588</v>
       </c>
       <c r="G30">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H30">
         <v>6</v>
@@ -10000,7 +10000,7 @@
         <v/>
       </c>
       <c r="L30">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="M30" t="str">
         <v/>
@@ -10026,22 +10026,22 @@
         <v>주</v>
       </c>
       <c r="C31">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="D31">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="E31">
-        <v>169</v>
+        <v>161.5</v>
       </c>
       <c r="F31">
-        <v>601</v>
+        <v>593.5</v>
       </c>
       <c r="G31">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I31">
         <v>0.5</v>
@@ -10053,7 +10053,7 @@
         <v/>
       </c>
       <c r="L31">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="M31" t="str">
         <v/>
@@ -10068,7 +10068,7 @@
         <v>운전자D</v>
       </c>
       <c r="Q31" t="str">
-        <v>작동유 온도 경고등 점등 후 소등(예시)</v>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -10079,22 +10079,22 @@
         <v>주</v>
       </c>
       <c r="C32">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="D32">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="E32">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="F32">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="G32">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I32">
         <v>0.5</v>
@@ -10106,7 +10106,7 @@
         <v/>
       </c>
       <c r="L32">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="M32" t="str">
         <v/>
@@ -10132,19 +10132,19 @@
         <v>주</v>
       </c>
       <c r="C33">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="D33">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="E33">
-        <v>182.5</v>
+        <v>173</v>
       </c>
       <c r="F33">
-        <v>614.5</v>
+        <v>605</v>
       </c>
       <c r="G33">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H33">
         <v>5</v>
@@ -10159,7 +10159,7 @@
         <v/>
       </c>
       <c r="L33">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="M33" t="str">
         <v/>
@@ -10185,22 +10185,22 @@
         <v>주</v>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="D34">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="E34">
-        <v>189.5</v>
+        <v>178.5</v>
       </c>
       <c r="F34">
-        <v>621.5</v>
+        <v>610.5</v>
       </c>
       <c r="G34">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I34">
         <v>0.5</v>
@@ -10212,7 +10212,7 @@
         <v/>
       </c>
       <c r="L34">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="M34" t="str">
         <v/>
@@ -10221,7 +10221,7 @@
         <v/>
       </c>
       <c r="O34" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P34" t="str">
         <v>운전자C</v>
@@ -10238,22 +10238,22 @@
         <v>주</v>
       </c>
       <c r="C35">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D35">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E35">
-        <v>197.5</v>
+        <v>184.5</v>
       </c>
       <c r="F35">
-        <v>629.5</v>
+        <v>616.5</v>
       </c>
       <c r="G35">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I35">
         <v>0.5</v>
@@ -10265,7 +10265,7 @@
         <v/>
       </c>
       <c r="L35">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M35" t="str">
         <v/>
@@ -10291,19 +10291,19 @@
         <v>주</v>
       </c>
       <c r="C36">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="D36">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="E36">
-        <v>204.5</v>
+        <v>191</v>
       </c>
       <c r="F36">
-        <v>636.5</v>
+        <v>623</v>
       </c>
       <c r="G36">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H36">
         <v>6</v>
@@ -10318,7 +10318,7 @@
         <v/>
       </c>
       <c r="L36">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="M36" t="str">
         <v/>
@@ -10327,13 +10327,13 @@
         <v/>
       </c>
       <c r="O36" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P36" t="str">
         <v>운전자A</v>
       </c>
       <c r="Q36" t="str">
-        <v/>
+        <v>충전 커넥터 체결 불량(예시)</v>
       </c>
     </row>
     <row r="37">
@@ -10344,19 +10344,19 @@
         <v>주</v>
       </c>
       <c r="C37">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="D37">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="E37">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="F37">
-        <v>642</v>
+        <v>629</v>
       </c>
       <c r="G37">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H37">
         <v>5</v>
@@ -10371,7 +10371,7 @@
         <v/>
       </c>
       <c r="L37">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="M37" t="str">
         <v/>
@@ -10397,22 +10397,22 @@
         <v>주</v>
       </c>
       <c r="C38">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="D38">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="E38">
-        <v>216.5</v>
+        <v>205</v>
       </c>
       <c r="F38">
-        <v>648.5</v>
+        <v>637</v>
       </c>
       <c r="G38">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I38">
         <v>0.5</v>
@@ -10424,7 +10424,7 @@
         <v/>
       </c>
       <c r="L38">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="M38" t="str">
         <v/>
@@ -10450,22 +10450,22 @@
         <v>주</v>
       </c>
       <c r="C39">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="D39">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="E39">
-        <v>221.5</v>
+        <v>212.5</v>
       </c>
       <c r="F39">
-        <v>653.5</v>
+        <v>644.5</v>
       </c>
       <c r="G39">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I39">
         <v>0.5</v>
@@ -10477,7 +10477,7 @@
         <v/>
       </c>
       <c r="L39">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="M39" t="str">
         <v/>
@@ -10503,19 +10503,19 @@
         <v>주</v>
       </c>
       <c r="C40">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="D40">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="E40">
-        <v>227</v>
+        <v>217.5</v>
       </c>
       <c r="F40">
-        <v>659</v>
+        <v>649.5</v>
       </c>
       <c r="G40">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H40">
         <v>5</v>
@@ -10530,7 +10530,7 @@
         <v/>
       </c>
       <c r="L40">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="M40" t="str">
         <v/>
@@ -10539,7 +10539,7 @@
         <v/>
       </c>
       <c r="O40" t="str">
-        <v>흐림</v>
+        <v>맑음</v>
       </c>
       <c r="P40" t="str">
         <v>운전자A</v>
@@ -10556,22 +10556,22 @@
         <v>주</v>
       </c>
       <c r="C41">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D41">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E41">
-        <v>233</v>
+        <v>225.5</v>
       </c>
       <c r="F41">
-        <v>665</v>
+        <v>657.5</v>
       </c>
       <c r="G41">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="H41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I41">
         <v>0.5</v>
@@ -10583,7 +10583,7 @@
         <v/>
       </c>
       <c r="L41">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M41" t="str">
         <v/>
@@ -10598,7 +10598,7 @@
         <v>운전자B</v>
       </c>
       <c r="Q41" t="str">
-        <v/>
+        <v>운전석 계기판 화면 깜빡임(예시)</v>
       </c>
     </row>
     <row r="42">
@@ -10609,22 +10609,22 @@
         <v>주</v>
       </c>
       <c r="C42">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D42">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="E42">
-        <v>239.5</v>
+        <v>231</v>
       </c>
       <c r="F42">
-        <v>671.5</v>
+        <v>663</v>
       </c>
       <c r="G42">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I42">
         <v>0.5</v>
@@ -10636,7 +10636,7 @@
         <v/>
       </c>
       <c r="L42">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="M42" t="str">
         <v/>
@@ -10645,13 +10645,13 @@
         <v/>
       </c>
       <c r="O42" t="str">
-        <v>흐림</v>
+        <v>맑음</v>
       </c>
       <c r="P42" t="str">
         <v>운전자C</v>
       </c>
       <c r="Q42" t="str">
-        <v>충전 커넥터 체결 불량(예시)</v>
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -10662,19 +10662,19 @@
         <v>주</v>
       </c>
       <c r="C43">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="D43">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="E43">
-        <v>245.5</v>
+        <v>236.5</v>
       </c>
       <c r="F43">
-        <v>677.5</v>
+        <v>668.5</v>
       </c>
       <c r="G43">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H43">
         <v>5</v>
@@ -10689,7 +10689,7 @@
         <v/>
       </c>
       <c r="L43">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="M43" t="str">
         <v/>
@@ -10704,7 +10704,7 @@
         <v>운전자D</v>
       </c>
       <c r="Q43" t="str">
-        <v/>
+        <v>브레이크 페달 유격 커짐(예시)</v>
       </c>
     </row>
     <row r="44">
@@ -10721,10 +10721,10 @@
         <v>8</v>
       </c>
       <c r="E44">
-        <v>253.5</v>
+        <v>244.5</v>
       </c>
       <c r="F44">
-        <v>685.5</v>
+        <v>676.5</v>
       </c>
       <c r="G44">
         <v>37</v>
@@ -10751,7 +10751,7 @@
         <v/>
       </c>
       <c r="O44" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P44" t="str">
         <v>운전자A</v>
@@ -10768,19 +10768,19 @@
         <v>주</v>
       </c>
       <c r="C45">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="D45">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="E45">
-        <v>261</v>
+        <v>252.5</v>
       </c>
       <c r="F45">
-        <v>693</v>
+        <v>684.5</v>
       </c>
       <c r="G45">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H45">
         <v>7</v>
@@ -10795,7 +10795,7 @@
         <v/>
       </c>
       <c r="L45">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="M45" t="str">
         <v/>
@@ -10810,7 +10810,7 @@
         <v>운전자B</v>
       </c>
       <c r="Q45" t="str">
-        <v/>
+        <v>브레이크 페달 유격 커짐(예시)</v>
       </c>
     </row>
     <row r="46">
@@ -10821,19 +10821,19 @@
         <v>주</v>
       </c>
       <c r="C46">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="D46">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="E46">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="F46">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="G46">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H46">
         <v>5</v>
@@ -10848,7 +10848,7 @@
         <v/>
       </c>
       <c r="L46">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="M46" t="str">
         <v/>
@@ -10857,7 +10857,7 @@
         <v/>
       </c>
       <c r="O46" t="str">
-        <v>맑음</v>
+        <v>비</v>
       </c>
       <c r="P46" t="str">
         <v>운전자C</v>
@@ -10874,22 +10874,22 @@
         <v>주</v>
       </c>
       <c r="C47">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D47">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E47">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="F47">
-        <v>706</v>
+        <v>696</v>
       </c>
       <c r="G47">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H47">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I47">
         <v>0.5</v>
@@ -10901,7 +10901,7 @@
         <v/>
       </c>
       <c r="L47">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M47" t="str">
         <v/>
@@ -10916,7 +10916,7 @@
         <v>운전자D</v>
       </c>
       <c r="Q47" t="str">
-        <v>운전석 계기판 화면 깜빡임(예시)</v>
+        <v/>
       </c>
     </row>
     <row r="48">
@@ -10927,22 +10927,22 @@
         <v>주</v>
       </c>
       <c r="C48">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="D48">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="E48">
-        <v>279.5</v>
+        <v>271.5</v>
       </c>
       <c r="F48">
-        <v>711.5</v>
+        <v>703.5</v>
       </c>
       <c r="G48">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H48">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I48">
         <v>0.5</v>
@@ -10954,7 +10954,7 @@
         <v/>
       </c>
       <c r="L48">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="M48" t="str">
         <v/>
@@ -10980,22 +10980,22 @@
         <v>주</v>
       </c>
       <c r="C49">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D49">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="E49">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="F49">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="G49">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H49">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I49">
         <v>0.5</v>
@@ -11007,7 +11007,7 @@
         <v/>
       </c>
       <c r="L49">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="M49" t="str">
         <v/>
@@ -11016,13 +11016,13 @@
         <v/>
       </c>
       <c r="O49" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P49" t="str">
         <v>운전자B</v>
       </c>
       <c r="Q49" t="str">
-        <v>브레이크 페달 유격 커짐(예시)</v>
+        <v/>
       </c>
     </row>
     <row r="50">
@@ -11033,22 +11033,22 @@
         <v>주</v>
       </c>
       <c r="C50">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D50">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E50">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F50">
-        <v>725</v>
+        <v>716</v>
       </c>
       <c r="G50">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H50">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I50">
         <v>0.5</v>
@@ -11060,7 +11060,7 @@
         <v/>
       </c>
       <c r="L50">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M50" t="str">
         <v/>
@@ -11069,7 +11069,7 @@
         <v/>
       </c>
       <c r="O50" t="str">
-        <v>흐림</v>
+        <v>비</v>
       </c>
       <c r="P50" t="str">
         <v>운전자C</v>
@@ -11086,22 +11086,22 @@
         <v>주</v>
       </c>
       <c r="C51">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D51">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E51">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="F51">
-        <v>733</v>
+        <v>723</v>
       </c>
       <c r="G51">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H51">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I51">
         <v>0.5</v>
@@ -11128,7 +11128,7 @@
         <v>운전자D</v>
       </c>
       <c r="Q51" t="str">
-        <v>브레이크 페달 유격 커짐(예시)</v>
+        <v/>
       </c>
     </row>
     <row r="52">
@@ -11139,22 +11139,22 @@
         <v>주</v>
       </c>
       <c r="C52">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="D52">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="E52">
-        <v>306.5</v>
+        <v>298</v>
       </c>
       <c r="F52">
-        <v>738.5</v>
+        <v>730</v>
       </c>
       <c r="G52">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H52">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I52">
         <v>0.5</v>
@@ -11175,7 +11175,7 @@
         <v/>
       </c>
       <c r="O52" t="str">
-        <v>비</v>
+        <v>맑음</v>
       </c>
       <c r="P52" t="str">
         <v>운전자A</v>
@@ -11192,22 +11192,22 @@
         <v>주</v>
       </c>
       <c r="C53">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D53">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E53">
-        <v>312.5</v>
+        <v>306</v>
       </c>
       <c r="F53">
-        <v>744.5</v>
+        <v>738</v>
       </c>
       <c r="G53">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="H53">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I53">
         <v>0.5</v>
@@ -11245,22 +11245,22 @@
         <v>주</v>
       </c>
       <c r="C54">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="D54">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="E54">
-        <v>320</v>
+        <v>312.5</v>
       </c>
       <c r="F54">
-        <v>752</v>
+        <v>744.5</v>
       </c>
       <c r="G54">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H54">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I54">
         <v>0.5</v>
@@ -11298,22 +11298,22 @@
         <v>주</v>
       </c>
       <c r="C55">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D55">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="E55">
-        <v>326.5</v>
+        <v>318</v>
       </c>
       <c r="F55">
-        <v>758.5</v>
+        <v>750</v>
       </c>
       <c r="G55">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I55">
         <v>0.5</v>
@@ -11357,10 +11357,10 @@
         <v>6</v>
       </c>
       <c r="E56">
-        <v>332.5</v>
+        <v>324</v>
       </c>
       <c r="F56">
-        <v>764.5</v>
+        <v>756</v>
       </c>
       <c r="G56">
         <v>28</v>
@@ -11404,22 +11404,22 @@
         <v>주</v>
       </c>
       <c r="C57">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="D57">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="E57">
-        <v>339.5</v>
+        <v>329.5</v>
       </c>
       <c r="F57">
-        <v>771.5</v>
+        <v>761.5</v>
       </c>
       <c r="G57">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H57">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I57">
         <v>0.5</v>
@@ -11440,7 +11440,7 @@
         <v/>
       </c>
       <c r="O57" t="str">
-        <v>맑음</v>
+        <v>비</v>
       </c>
       <c r="P57" t="str">
         <v>운전자B</v>
@@ -11457,19 +11457,19 @@
         <v>주</v>
       </c>
       <c r="C58">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="D58">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="E58">
-        <v>346.5</v>
+        <v>336</v>
       </c>
       <c r="F58">
-        <v>778.5</v>
+        <v>768</v>
       </c>
       <c r="G58">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H58">
         <v>6</v>
@@ -11510,19 +11510,19 @@
         <v>주</v>
       </c>
       <c r="C59">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="D59">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="E59">
-        <v>354.5</v>
+        <v>343.5</v>
       </c>
       <c r="F59">
-        <v>786.5</v>
+        <v>775.5</v>
       </c>
       <c r="G59">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H59">
         <v>7</v>
@@ -11569,10 +11569,10 @@
         <v>6.5</v>
       </c>
       <c r="E60">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="F60">
-        <v>793</v>
+        <v>782</v>
       </c>
       <c r="G60">
         <v>30</v>
@@ -11599,7 +11599,7 @@
         <v/>
       </c>
       <c r="O60" t="str">
-        <v>맑음</v>
+        <v>흐림</v>
       </c>
       <c r="P60" t="str">
         <v>운전자A</v>
@@ -11616,19 +11616,19 @@
         <v>주</v>
       </c>
       <c r="C61">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="D61">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="E61">
-        <v>366.5</v>
+        <v>355</v>
       </c>
       <c r="F61">
-        <v>798.5</v>
+        <v>787</v>
       </c>
       <c r="G61">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H61">
         <v>5</v>
@@ -11669,19 +11669,19 @@
         <v>주</v>
       </c>
       <c r="C62">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="D62">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="E62">
-        <v>372.5</v>
+        <v>360.5</v>
       </c>
       <c r="F62">
-        <v>804.5</v>
+        <v>792.5</v>
       </c>
       <c r="G62">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H62">
         <v>5</v>
@@ -11722,22 +11722,22 @@
         <v>주</v>
       </c>
       <c r="C63">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D63">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="E63">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="F63">
-        <v>810</v>
+        <v>799</v>
       </c>
       <c r="G63">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H63">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I63">
         <v>0.5</v>
@@ -11781,10 +11781,10 @@
         <v>6.5</v>
       </c>
       <c r="E64">
-        <v>384.5</v>
+        <v>373.5</v>
       </c>
       <c r="F64">
-        <v>816.5</v>
+        <v>805.5</v>
       </c>
       <c r="G64">
         <v>30</v>
@@ -11828,22 +11828,22 @@
         <v>주</v>
       </c>
       <c r="C65">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="D65">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="E65">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="F65">
-        <v>824</v>
+        <v>811</v>
       </c>
       <c r="G65">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H65">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I65">
         <v>0.5</v>
@@ -11881,22 +11881,22 @@
         <v>주</v>
       </c>
       <c r="C66">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="D66">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="E66">
-        <v>398.5</v>
+        <v>385</v>
       </c>
       <c r="F66">
-        <v>830.5</v>
+        <v>817</v>
       </c>
       <c r="G66">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H66">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I66">
         <v>0.5</v>
@@ -11917,7 +11917,7 @@
         <v/>
       </c>
       <c r="O66" t="str">
-        <v>흐림</v>
+        <v>비</v>
       </c>
       <c r="P66" t="str">
         <v>운전자C</v>
@@ -11934,22 +11934,22 @@
         <v>주</v>
       </c>
       <c r="C67">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="D67">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="E67">
-        <v>403.5</v>
+        <v>391.5</v>
       </c>
       <c r="F67">
-        <v>835.5</v>
+        <v>823.5</v>
       </c>
       <c r="G67">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I67">
         <v>0.5</v>
@@ -11970,7 +11970,7 @@
         <v/>
       </c>
       <c r="O67" t="str">
-        <v>흐림</v>
+        <v>맑음</v>
       </c>
       <c r="P67" t="str">
         <v>운전자D</v>
@@ -11987,22 +11987,22 @@
         <v>주</v>
       </c>
       <c r="C68">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D68">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="E68">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="F68">
-        <v>841</v>
+        <v>830</v>
       </c>
       <c r="G68">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H68">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I68">
         <v>0.5</v>
@@ -12023,13 +12023,13 @@
         <v/>
       </c>
       <c r="O68" t="str">
-        <v>비</v>
+        <v>흐림</v>
       </c>
       <c r="P68" t="str">
         <v>운전자A</v>
       </c>
       <c r="Q68" t="str">
-        <v/>
+        <v>브레이크 페달 유격 커짐(예시)</v>
       </c>
     </row>
     <row r="69">
@@ -12040,22 +12040,22 @@
         <v>주</v>
       </c>
       <c r="C69">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="D69">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="E69">
-        <v>415.5</v>
+        <v>403</v>
       </c>
       <c r="F69">
-        <v>847.5</v>
+        <v>835</v>
       </c>
       <c r="G69">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I69">
         <v>0.5</v>
@@ -12076,7 +12076,7 @@
         <v/>
       </c>
       <c r="O69" t="str">
-        <v>비</v>
+        <v>맑음</v>
       </c>
       <c r="P69" t="str">
         <v>운전자B</v>
